--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -3980,10 +3980,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118683782</v>
+        <v>118682931</v>
       </c>
       <c r="B33" t="n">
-        <v>79073</v>
+        <v>91779</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3992,41 +3992,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696753</v>
+        <v>697001</v>
       </c>
       <c r="R33" t="n">
-        <v>7323615</v>
+        <v>7323764</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4070,12 +4070,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4086,10 +4086,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118683006</v>
+        <v>118682935</v>
       </c>
       <c r="B34" t="n">
-        <v>79073</v>
+        <v>91779</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4098,41 +4098,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696855</v>
+        <v>696866</v>
       </c>
       <c r="R34" t="n">
-        <v>7323504</v>
+        <v>7323727</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4170,19 +4170,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4193,10 +4192,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118686843</v>
+        <v>118672140</v>
       </c>
       <c r="B35" t="n">
-        <v>80441</v>
+        <v>91779</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4205,41 +4204,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696934</v>
+        <v>697004</v>
       </c>
       <c r="R35" t="n">
-        <v>7323591</v>
+        <v>7323588</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4283,12 +4282,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4299,10 +4298,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118683793</v>
+        <v>118683831</v>
       </c>
       <c r="B36" t="n">
-        <v>78566</v>
+        <v>77868</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4315,21 +4314,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>864</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4339,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696783</v>
+        <v>696737</v>
       </c>
       <c r="R36" t="n">
-        <v>7323644</v>
+        <v>7323611</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4405,7 +4404,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118683831</v>
+        <v>118682823</v>
       </c>
       <c r="B37" t="n">
         <v>77868</v>
@@ -4441,14 +4440,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696737</v>
+        <v>697077</v>
       </c>
       <c r="R37" t="n">
-        <v>7323611</v>
+        <v>7323757</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4495,12 +4494,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4511,7 +4510,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118682823</v>
+        <v>118683821</v>
       </c>
       <c r="B38" t="n">
         <v>77868</v>
@@ -4547,14 +4546,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>697077</v>
+        <v>697026</v>
       </c>
       <c r="R38" t="n">
-        <v>7323757</v>
+        <v>7323766</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4601,12 +4600,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4617,10 +4616,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118683821</v>
+        <v>118683807</v>
       </c>
       <c r="B39" t="n">
-        <v>77868</v>
+        <v>77416</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4633,21 +4632,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4657,10 +4656,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>697026</v>
+        <v>696830</v>
       </c>
       <c r="R39" t="n">
-        <v>7323766</v>
+        <v>7323581</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4723,10 +4722,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118683800</v>
+        <v>118683782</v>
       </c>
       <c r="B40" t="n">
-        <v>78129</v>
+        <v>79073</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4739,21 +4738,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4763,10 +4762,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>697097</v>
+        <v>696753</v>
       </c>
       <c r="R40" t="n">
-        <v>7323699</v>
+        <v>7323615</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4829,10 +4828,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118682931</v>
+        <v>118683006</v>
       </c>
       <c r="B41" t="n">
-        <v>91779</v>
+        <v>79073</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4841,41 +4840,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>697001</v>
+        <v>696855</v>
       </c>
       <c r="R41" t="n">
-        <v>7323764</v>
+        <v>7323504</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4913,18 +4912,19 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4935,10 +4935,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118682935</v>
+        <v>118683800</v>
       </c>
       <c r="B42" t="n">
-        <v>91779</v>
+        <v>78129</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4947,41 +4947,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696866</v>
+        <v>697097</v>
       </c>
       <c r="R42" t="n">
-        <v>7323727</v>
+        <v>7323699</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5025,12 +5025,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5041,10 +5041,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118672140</v>
+        <v>118686843</v>
       </c>
       <c r="B43" t="n">
-        <v>91779</v>
+        <v>80441</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5053,41 +5053,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>697004</v>
+        <v>696934</v>
       </c>
       <c r="R43" t="n">
-        <v>7323588</v>
+        <v>7323591</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5131,12 +5131,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5147,10 +5147,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118683807</v>
+        <v>118683793</v>
       </c>
       <c r="B44" t="n">
-        <v>77416</v>
+        <v>78566</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5163,21 +5163,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6487</v>
+        <v>864</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696830</v>
+        <v>696783</v>
       </c>
       <c r="R44" t="n">
-        <v>7323581</v>
+        <v>7323644</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118671198</v>
+        <v>118670735</v>
       </c>
       <c r="B60" t="n">
-        <v>79073</v>
+        <v>91779</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6858,38 +6858,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Anna-Lisabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>696727</v>
+        <v>696724</v>
       </c>
       <c r="R60" t="n">
-        <v>7323649</v>
+        <v>7323610</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6952,10 +6952,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118670735</v>
+        <v>118682941</v>
       </c>
       <c r="B61" t="n">
-        <v>91779</v>
+        <v>91773</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6964,38 +6964,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696724</v>
+        <v>696974</v>
       </c>
       <c r="R61" t="n">
-        <v>7323610</v>
+        <v>7323700</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7042,12 +7042,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7058,10 +7058,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118682941</v>
+        <v>118683815</v>
       </c>
       <c r="B62" t="n">
-        <v>91773</v>
+        <v>77868</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7074,37 +7074,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696974</v>
+        <v>697006</v>
       </c>
       <c r="R62" t="n">
-        <v>7323700</v>
+        <v>7323539</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7148,12 +7148,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7164,7 +7164,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118683815</v>
+        <v>118683022</v>
       </c>
       <c r="B63" t="n">
         <v>77868</v>
@@ -7200,14 +7200,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>697006</v>
+        <v>697008</v>
       </c>
       <c r="R63" t="n">
-        <v>7323539</v>
+        <v>7323621</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7248,18 +7248,19 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7270,10 +7271,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118683022</v>
+        <v>118683017</v>
       </c>
       <c r="B64" t="n">
-        <v>77868</v>
+        <v>77416</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7286,21 +7287,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7310,10 +7311,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>697008</v>
+        <v>697052</v>
       </c>
       <c r="R64" t="n">
-        <v>7323621</v>
+        <v>7323652</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7354,7 +7355,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7377,10 +7377,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118683017</v>
+        <v>118671198</v>
       </c>
       <c r="B65" t="n">
-        <v>77416</v>
+        <v>79073</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7393,37 +7393,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>697052</v>
+        <v>696727</v>
       </c>
       <c r="R65" t="n">
-        <v>7323652</v>
+        <v>7323649</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7467,12 +7467,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7589,10 +7589,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118682692</v>
+        <v>118682704</v>
       </c>
       <c r="B67" t="n">
-        <v>90469</v>
+        <v>90504</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7601,25 +7601,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>696974</v>
+        <v>696960</v>
       </c>
       <c r="R67" t="n">
-        <v>7323636</v>
+        <v>7323635</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7695,10 +7695,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118683816</v>
+        <v>118683015</v>
       </c>
       <c r="B68" t="n">
-        <v>77868</v>
+        <v>77416</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7711,34 +7711,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>697029</v>
+        <v>696832</v>
       </c>
       <c r="R68" t="n">
-        <v>7323565</v>
+        <v>7323503</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7785,12 +7785,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7801,10 +7801,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118684523</v>
+        <v>118684515</v>
       </c>
       <c r="B69" t="n">
-        <v>77868</v>
+        <v>79102</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7817,21 +7817,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696848</v>
+        <v>696823</v>
       </c>
       <c r="R69" t="n">
-        <v>7323640</v>
+        <v>7323553</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7907,10 +7907,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118683015</v>
+        <v>118683762</v>
       </c>
       <c r="B70" t="n">
-        <v>77416</v>
+        <v>79102</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7923,34 +7923,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696832</v>
+        <v>697090</v>
       </c>
       <c r="R70" t="n">
-        <v>7323503</v>
+        <v>7323699</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7997,12 +7997,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8013,10 +8013,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118684515</v>
+        <v>118670832</v>
       </c>
       <c r="B71" t="n">
-        <v>79102</v>
+        <v>91773</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8029,34 +8029,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>696823</v>
+        <v>696711</v>
       </c>
       <c r="R71" t="n">
-        <v>7323553</v>
+        <v>7323645</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8103,12 +8103,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8119,10 +8119,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118683762</v>
+        <v>118682717</v>
       </c>
       <c r="B72" t="n">
-        <v>79102</v>
+        <v>91773</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8135,37 +8135,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>697090</v>
+        <v>696852</v>
       </c>
       <c r="R72" t="n">
-        <v>7323699</v>
+        <v>7323640</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8209,12 +8209,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8225,10 +8225,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118682704</v>
+        <v>118682691</v>
       </c>
       <c r="B73" t="n">
-        <v>90504</v>
+        <v>90430</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8241,21 +8241,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>3242</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8265,10 +8265,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696960</v>
+        <v>696809</v>
       </c>
       <c r="R73" t="n">
-        <v>7323635</v>
+        <v>7323644</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8331,10 +8331,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118670832</v>
+        <v>118682692</v>
       </c>
       <c r="B74" t="n">
-        <v>91773</v>
+        <v>90469</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8343,38 +8343,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4362</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696711</v>
+        <v>696974</v>
       </c>
       <c r="R74" t="n">
-        <v>7323645</v>
+        <v>7323636</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8421,12 +8421,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8437,10 +8437,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118682717</v>
+        <v>118683816</v>
       </c>
       <c r="B75" t="n">
-        <v>91773</v>
+        <v>77868</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8453,37 +8453,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696852</v>
+        <v>697029</v>
       </c>
       <c r="R75" t="n">
-        <v>7323640</v>
+        <v>7323565</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8527,12 +8527,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8543,10 +8543,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118682691</v>
+        <v>118684523</v>
       </c>
       <c r="B76" t="n">
-        <v>90430</v>
+        <v>77868</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8559,34 +8559,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3242</v>
+        <v>6437</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696809</v>
+        <v>696848</v>
       </c>
       <c r="R76" t="n">
-        <v>7323644</v>
+        <v>7323640</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8633,12 +8633,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8649,10 +8649,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118683775</v>
+        <v>118683023</v>
       </c>
       <c r="B77" t="n">
-        <v>79073</v>
+        <v>77868</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8665,34 +8665,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>697098</v>
+        <v>697097</v>
       </c>
       <c r="R77" t="n">
-        <v>7323697</v>
+        <v>7323675</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8733,18 +8733,19 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8755,10 +8756,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118682771</v>
+        <v>118686836</v>
       </c>
       <c r="B78" t="n">
-        <v>89575</v>
+        <v>79102</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8771,37 +8772,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>697008</v>
+        <v>696835</v>
       </c>
       <c r="R78" t="n">
-        <v>7323675</v>
+        <v>7323611</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8839,19 +8840,18 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8862,10 +8862,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118683791</v>
+        <v>118683758</v>
       </c>
       <c r="B79" t="n">
-        <v>80441</v>
+        <v>79102</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8878,21 +8878,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8902,10 +8902,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696808</v>
+        <v>696843</v>
       </c>
       <c r="R79" t="n">
-        <v>7323509</v>
+        <v>7323526</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8968,7 +8968,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118686836</v>
+        <v>118683004</v>
       </c>
       <c r="B80" t="n">
         <v>79102</v>
@@ -9004,17 +9004,17 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696835</v>
+        <v>696832</v>
       </c>
       <c r="R80" t="n">
-        <v>7323611</v>
+        <v>7323503</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9058,12 +9058,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9074,7 +9074,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118683758</v>
+        <v>118683760</v>
       </c>
       <c r="B81" t="n">
         <v>79102</v>
@@ -9114,10 +9114,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>696843</v>
+        <v>696860</v>
       </c>
       <c r="R81" t="n">
-        <v>7323526</v>
+        <v>7323545</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9180,10 +9180,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118683004</v>
+        <v>118683784</v>
       </c>
       <c r="B82" t="n">
-        <v>79102</v>
+        <v>96807</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9192,38 +9192,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>696832</v>
+        <v>696996</v>
       </c>
       <c r="R82" t="n">
-        <v>7323503</v>
+        <v>7323706</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9270,12 +9270,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9286,10 +9286,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118683760</v>
+        <v>118683775</v>
       </c>
       <c r="B83" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9302,21 +9302,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9326,10 +9326,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>696860</v>
+        <v>697098</v>
       </c>
       <c r="R83" t="n">
-        <v>7323545</v>
+        <v>7323697</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9392,10 +9392,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118683023</v>
+        <v>118682771</v>
       </c>
       <c r="B84" t="n">
-        <v>77868</v>
+        <v>89575</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9408,31 +9408,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6437</v>
+        <v>1962</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>697097</v>
+        <v>697008</v>
       </c>
       <c r="R84" t="n">
         <v>7323675</v>
@@ -9483,12 +9483,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9499,10 +9499,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118683784</v>
+        <v>118683791</v>
       </c>
       <c r="B85" t="n">
-        <v>96807</v>
+        <v>80441</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9511,25 +9511,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221941</v>
+        <v>1049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9539,10 +9539,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>696996</v>
+        <v>696808</v>
       </c>
       <c r="R85" t="n">
-        <v>7323706</v>
+        <v>7323509</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -12786,10 +12786,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118682706</v>
+        <v>118683804</v>
       </c>
       <c r="B116" t="n">
-        <v>90654</v>
+        <v>78129</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12798,41 +12798,41 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>697014</v>
+        <v>696768</v>
       </c>
       <c r="R116" t="n">
-        <v>7323674</v>
+        <v>7323612</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12876,12 +12876,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12892,7 +12892,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118682708</v>
+        <v>118682706</v>
       </c>
       <c r="B117" t="n">
         <v>90654</v>
@@ -12932,10 +12932,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>696767</v>
+        <v>697014</v>
       </c>
       <c r="R117" t="n">
-        <v>7323634</v>
+        <v>7323674</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12998,10 +12998,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118683783</v>
+        <v>118682708</v>
       </c>
       <c r="B118" t="n">
-        <v>80441</v>
+        <v>90654</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13010,41 +13010,41 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1049</v>
+        <v>1503</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>696830</v>
+        <v>696767</v>
       </c>
       <c r="R118" t="n">
-        <v>7323581</v>
+        <v>7323634</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13088,12 +13088,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -13104,10 +13104,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118682716</v>
+        <v>118683783</v>
       </c>
       <c r="B119" t="n">
-        <v>91773</v>
+        <v>80441</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13120,37 +13120,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4362</v>
+        <v>1049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>697029</v>
+        <v>696830</v>
       </c>
       <c r="R119" t="n">
-        <v>7323654</v>
+        <v>7323581</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13194,12 +13194,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -13210,10 +13210,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118683804</v>
+        <v>118671206</v>
       </c>
       <c r="B120" t="n">
-        <v>78129</v>
+        <v>91779</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13222,41 +13222,41 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>696768</v>
+        <v>696766</v>
       </c>
       <c r="R120" t="n">
-        <v>7323612</v>
+        <v>7323608</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13300,12 +13300,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13316,10 +13316,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118671206</v>
+        <v>118682716</v>
       </c>
       <c r="B121" t="n">
-        <v>91779</v>
+        <v>91773</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13328,38 +13328,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>696766</v>
+        <v>697029</v>
       </c>
       <c r="R121" t="n">
-        <v>7323608</v>
+        <v>7323654</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13406,12 +13406,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13847,10 +13847,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118683806</v>
+        <v>118682930</v>
       </c>
       <c r="B126" t="n">
-        <v>77416</v>
+        <v>90749</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13859,41 +13859,41 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6487</v>
+        <v>65</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>696963</v>
+        <v>696846</v>
       </c>
       <c r="R126" t="n">
-        <v>7323687</v>
+        <v>7323664</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13937,12 +13937,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13953,10 +13953,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118682921</v>
+        <v>118682932</v>
       </c>
       <c r="B127" t="n">
-        <v>79073</v>
+        <v>91779</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13965,25 +13965,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13993,10 +13993,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>696716</v>
+        <v>696873</v>
       </c>
       <c r="R127" t="n">
-        <v>7323625</v>
+        <v>7323783</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14048,7 +14048,7 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -14059,10 +14059,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118683770</v>
+        <v>118682939</v>
       </c>
       <c r="B128" t="n">
-        <v>79073</v>
+        <v>91779</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14071,41 +14071,41 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>696916</v>
+        <v>696750</v>
       </c>
       <c r="R128" t="n">
-        <v>7323554</v>
+        <v>7323661</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14149,12 +14149,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -14165,10 +14165,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118682930</v>
+        <v>118683806</v>
       </c>
       <c r="B129" t="n">
-        <v>90749</v>
+        <v>77416</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14177,41 +14177,41 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>65</v>
+        <v>6487</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>696846</v>
+        <v>696963</v>
       </c>
       <c r="R129" t="n">
-        <v>7323664</v>
+        <v>7323687</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14255,12 +14255,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14271,10 +14271,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118682932</v>
+        <v>118673032</v>
       </c>
       <c r="B130" t="n">
-        <v>91779</v>
+        <v>90524</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14283,38 +14283,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>696873</v>
+        <v>696724</v>
       </c>
       <c r="R130" t="n">
-        <v>7323783</v>
+        <v>7323610</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14361,12 +14361,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14377,10 +14377,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118682939</v>
+        <v>118682827</v>
       </c>
       <c r="B131" t="n">
-        <v>91779</v>
+        <v>77868</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14389,41 +14389,41 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>696750</v>
+        <v>696890</v>
       </c>
       <c r="R131" t="n">
-        <v>7323661</v>
+        <v>7323617</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14467,12 +14467,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14483,10 +14483,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118673032</v>
+        <v>118682945</v>
       </c>
       <c r="B132" t="n">
-        <v>90524</v>
+        <v>77868</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14499,34 +14499,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5442</v>
+        <v>6437</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>696724</v>
+        <v>696772</v>
       </c>
       <c r="R132" t="n">
-        <v>7323610</v>
+        <v>7323668</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14573,12 +14573,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14589,10 +14589,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118682827</v>
+        <v>118683768</v>
       </c>
       <c r="B133" t="n">
-        <v>77868</v>
+        <v>79102</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14605,34 +14605,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>696890</v>
+        <v>696728</v>
       </c>
       <c r="R133" t="n">
-        <v>7323617</v>
+        <v>7323627</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -14679,12 +14679,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -14695,10 +14695,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118682945</v>
+        <v>118682921</v>
       </c>
       <c r="B134" t="n">
-        <v>77868</v>
+        <v>79073</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14711,21 +14711,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14735,10 +14735,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>696772</v>
+        <v>696716</v>
       </c>
       <c r="R134" t="n">
-        <v>7323668</v>
+        <v>7323625</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14801,10 +14801,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118683768</v>
+        <v>118683770</v>
       </c>
       <c r="B135" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14817,21 +14817,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14841,10 +14841,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>696728</v>
+        <v>696916</v>
       </c>
       <c r="R135" t="n">
-        <v>7323627</v>
+        <v>7323554</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -16815,10 +16815,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118683802</v>
+        <v>118683779</v>
       </c>
       <c r="B154" t="n">
-        <v>78129</v>
+        <v>79073</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16831,21 +16831,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16855,10 +16855,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>696995</v>
+        <v>696901</v>
       </c>
       <c r="R154" t="n">
-        <v>7323745</v>
+        <v>7323660</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -16921,10 +16921,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118683799</v>
+        <v>118686837</v>
       </c>
       <c r="B155" t="n">
-        <v>78129</v>
+        <v>79073</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16937,37 +16937,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>697022</v>
+        <v>696859</v>
       </c>
       <c r="R155" t="n">
-        <v>7323625</v>
+        <v>7323641</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17011,12 +17011,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -17027,10 +17027,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>118683018</v>
+        <v>118683009</v>
       </c>
       <c r="B156" t="n">
-        <v>77416</v>
+        <v>79073</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17043,21 +17043,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17133,10 +17133,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118683019</v>
+        <v>118683802</v>
       </c>
       <c r="B157" t="n">
-        <v>77416</v>
+        <v>78129</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17149,34 +17149,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>697090</v>
+        <v>696995</v>
       </c>
       <c r="R157" t="n">
-        <v>7323674</v>
+        <v>7323745</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -17217,19 +17217,18 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -17240,10 +17239,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118683792</v>
+        <v>118683799</v>
       </c>
       <c r="B158" t="n">
-        <v>80441</v>
+        <v>78129</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17256,21 +17255,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17280,10 +17279,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>696903</v>
+        <v>697022</v>
       </c>
       <c r="R158" t="n">
-        <v>7323655</v>
+        <v>7323625</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -17346,10 +17345,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118671603</v>
+        <v>118683028</v>
       </c>
       <c r="B159" t="n">
-        <v>90654</v>
+        <v>77868</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17358,41 +17357,41 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>696861</v>
+        <v>696825</v>
       </c>
       <c r="R159" t="n">
-        <v>7323661</v>
+        <v>7323668</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17430,28 +17429,33 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY159" t="inlineStr"/>
+          <t>Torun Ingrid Maria Jacobsson</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>118672105</v>
+        <v>118683830</v>
       </c>
       <c r="B160" t="n">
-        <v>91773</v>
+        <v>77868</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17464,37 +17468,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>696962</v>
+        <v>696752</v>
       </c>
       <c r="R160" t="n">
-        <v>7323622</v>
+        <v>7323618</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17538,12 +17542,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -17554,7 +17558,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>118683028</v>
+        <v>118682944</v>
       </c>
       <c r="B161" t="n">
         <v>77868</v>
@@ -17590,17 +17594,17 @@
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>696825</v>
+        <v>696872</v>
       </c>
       <c r="R161" t="n">
-        <v>7323668</v>
+        <v>7323693</v>
       </c>
       <c r="S161" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17638,19 +17642,18 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -17661,10 +17664,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>118683830</v>
+        <v>118683786</v>
       </c>
       <c r="B162" t="n">
-        <v>77868</v>
+        <v>78510</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17673,25 +17676,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17701,10 +17704,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>696752</v>
+        <v>696838</v>
       </c>
       <c r="R162" t="n">
-        <v>7323618</v>
+        <v>7323602</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -17767,7 +17770,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>118682944</v>
+        <v>118673264</v>
       </c>
       <c r="B163" t="n">
         <v>77868</v>
@@ -17803,14 +17806,14 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>696872</v>
+        <v>696724</v>
       </c>
       <c r="R163" t="n">
-        <v>7323693</v>
+        <v>7323610</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17857,12 +17860,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -17873,10 +17876,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>118683786</v>
+        <v>118682826</v>
       </c>
       <c r="B164" t="n">
-        <v>78510</v>
+        <v>77868</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17885,38 +17888,38 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6434</v>
+        <v>6437</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>696838</v>
+        <v>696936</v>
       </c>
       <c r="R164" t="n">
-        <v>7323602</v>
+        <v>7323719</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -17963,12 +17966,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -17979,10 +17982,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>118673264</v>
+        <v>118683792</v>
       </c>
       <c r="B165" t="n">
-        <v>77868</v>
+        <v>80441</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17995,37 +17998,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6437</v>
+        <v>1049</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>696724</v>
+        <v>696903</v>
       </c>
       <c r="R165" t="n">
-        <v>7323610</v>
+        <v>7323655</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18069,12 +18072,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -18085,10 +18088,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>118682826</v>
+        <v>118671603</v>
       </c>
       <c r="B166" t="n">
-        <v>77868</v>
+        <v>90654</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18097,41 +18100,41 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>696936</v>
+        <v>696861</v>
       </c>
       <c r="R166" t="n">
-        <v>7323719</v>
+        <v>7323661</v>
       </c>
       <c r="S166" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18175,26 +18178,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
-        </is>
-      </c>
-      <c r="AY166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>118683779</v>
+        <v>118672105</v>
       </c>
       <c r="B167" t="n">
-        <v>79073</v>
+        <v>91773</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18207,37 +18206,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>696901</v>
+        <v>696962</v>
       </c>
       <c r="R167" t="n">
-        <v>7323660</v>
+        <v>7323622</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18281,12 +18280,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -18297,10 +18296,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>118686837</v>
+        <v>118683018</v>
       </c>
       <c r="B168" t="n">
-        <v>79073</v>
+        <v>77416</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18313,37 +18312,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>696859</v>
+        <v>697057</v>
       </c>
       <c r="R168" t="n">
-        <v>7323641</v>
+        <v>7323625</v>
       </c>
       <c r="S168" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18387,12 +18386,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -18403,10 +18402,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>118683009</v>
+        <v>118683019</v>
       </c>
       <c r="B169" t="n">
-        <v>79073</v>
+        <v>77416</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18419,21 +18418,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18443,10 +18442,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>697057</v>
+        <v>697090</v>
       </c>
       <c r="R169" t="n">
-        <v>7323625</v>
+        <v>7323674</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -18487,6 +18486,7 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -20951,10 +20951,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>118682712</v>
+        <v>118683012</v>
       </c>
       <c r="B193" t="n">
-        <v>91779</v>
+        <v>96807</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20967,37 +20967,37 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>697018</v>
+        <v>696956</v>
       </c>
       <c r="R193" t="n">
-        <v>7323682</v>
+        <v>7323675</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21041,12 +21041,12 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -21481,10 +21481,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>118684517</v>
+        <v>118683764</v>
       </c>
       <c r="B198" t="n">
-        <v>56502</v>
+        <v>79102</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21493,41 +21493,41 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>697021</v>
+        <v>697005</v>
       </c>
       <c r="R198" t="n">
-        <v>7323671</v>
+        <v>7323759</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21571,12 +21571,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -21587,7 +21587,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>118683764</v>
+        <v>118682918</v>
       </c>
       <c r="B199" t="n">
         <v>79102</v>
@@ -21623,17 +21623,17 @@
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>697005</v>
+        <v>696716</v>
       </c>
       <c r="R199" t="n">
-        <v>7323759</v>
+        <v>7323623</v>
       </c>
       <c r="S199" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21677,12 +21677,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -21693,10 +21693,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>118682918</v>
+        <v>118684517</v>
       </c>
       <c r="B200" t="n">
-        <v>79102</v>
+        <v>56502</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21705,38 +21705,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>696716</v>
+        <v>697021</v>
       </c>
       <c r="R200" t="n">
-        <v>7323623</v>
+        <v>7323671</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21783,12 +21783,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -21799,10 +21799,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>118683012</v>
+        <v>118682712</v>
       </c>
       <c r="B201" t="n">
-        <v>96807</v>
+        <v>91779</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21815,37 +21815,37 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>696956</v>
+        <v>697018</v>
       </c>
       <c r="R201" t="n">
-        <v>7323675</v>
+        <v>7323682</v>
       </c>
       <c r="S201" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21889,12 +21889,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -22648,10 +22648,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>118682818</v>
+        <v>118683776</v>
       </c>
       <c r="B209" t="n">
-        <v>91779</v>
+        <v>79073</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22660,38 +22660,38 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>696942</v>
+        <v>697001</v>
       </c>
       <c r="R209" t="n">
-        <v>7323751</v>
+        <v>7323753</v>
       </c>
       <c r="S209" t="n">
         <v>15</v>
@@ -22738,12 +22738,12 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
@@ -22754,10 +22754,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>118682821</v>
+        <v>118683008</v>
       </c>
       <c r="B210" t="n">
-        <v>77868</v>
+        <v>79073</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22770,34 +22770,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>696870</v>
+        <v>697097</v>
       </c>
       <c r="R210" t="n">
-        <v>7323489</v>
+        <v>7323675</v>
       </c>
       <c r="S210" t="n">
         <v>15</v>
@@ -22838,18 +22838,19 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
@@ -22860,10 +22861,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>118683024</v>
+        <v>118683803</v>
       </c>
       <c r="B211" t="n">
-        <v>77868</v>
+        <v>78129</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22876,34 +22877,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>696964</v>
+        <v>696849</v>
       </c>
       <c r="R211" t="n">
-        <v>7323642</v>
+        <v>7323646</v>
       </c>
       <c r="S211" t="n">
         <v>15</v>
@@ -22944,19 +22945,18 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
@@ -22967,10 +22967,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>118670883</v>
+        <v>118673080</v>
       </c>
       <c r="B212" t="n">
-        <v>77868</v>
+        <v>91773</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22983,34 +22983,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6437</v>
+        <v>4362</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Anna-Lisabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>696727</v>
+        <v>696724</v>
       </c>
       <c r="R212" t="n">
-        <v>7323657</v>
+        <v>7323610</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23073,10 +23073,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>118683776</v>
+        <v>118682818</v>
       </c>
       <c r="B213" t="n">
-        <v>79073</v>
+        <v>91779</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -23085,38 +23085,38 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>697001</v>
+        <v>696942</v>
       </c>
       <c r="R213" t="n">
-        <v>7323753</v>
+        <v>7323751</v>
       </c>
       <c r="S213" t="n">
         <v>15</v>
@@ -23163,12 +23163,12 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
@@ -23179,10 +23179,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>118683008</v>
+        <v>118682821</v>
       </c>
       <c r="B214" t="n">
-        <v>79073</v>
+        <v>77868</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23195,34 +23195,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>697097</v>
+        <v>696870</v>
       </c>
       <c r="R214" t="n">
-        <v>7323675</v>
+        <v>7323489</v>
       </c>
       <c r="S214" t="n">
         <v>15</v>
@@ -23263,19 +23263,18 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
-      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
@@ -23286,10 +23285,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>118683803</v>
+        <v>118683024</v>
       </c>
       <c r="B215" t="n">
-        <v>78129</v>
+        <v>77868</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -23302,34 +23301,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>696849</v>
+        <v>696964</v>
       </c>
       <c r="R215" t="n">
-        <v>7323646</v>
+        <v>7323642</v>
       </c>
       <c r="S215" t="n">
         <v>15</v>
@@ -23370,18 +23369,19 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
+      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
@@ -23392,10 +23392,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>118673080</v>
+        <v>118670883</v>
       </c>
       <c r="B216" t="n">
-        <v>91773</v>
+        <v>77868</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -23408,34 +23408,34 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>696724</v>
+        <v>696727</v>
       </c>
       <c r="R216" t="n">
-        <v>7323610</v>
+        <v>7323657</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118683758</v>
+        <v>118683827</v>
       </c>
       <c r="B12" t="n">
-        <v>79102</v>
+        <v>77868</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,21 +1759,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696843</v>
+        <v>696832</v>
       </c>
       <c r="R12" t="n">
-        <v>7323526</v>
+        <v>7323578</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1849,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118682713</v>
+        <v>118683826</v>
       </c>
       <c r="B13" t="n">
-        <v>91779</v>
+        <v>77868</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,41 +1861,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696803</v>
+        <v>696900</v>
       </c>
       <c r="R13" t="n">
-        <v>7323628</v>
+        <v>7323650</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1939,12 +1939,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1955,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118671533</v>
+        <v>118684523</v>
       </c>
       <c r="B14" t="n">
-        <v>89906</v>
+        <v>77868</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,38 +1967,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5685</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696845</v>
+        <v>696848</v>
       </c>
       <c r="R14" t="n">
-        <v>7323632</v>
+        <v>7323640</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,12 +2045,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2061,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118683799</v>
+        <v>118683022</v>
       </c>
       <c r="B15" t="n">
-        <v>78129</v>
+        <v>77868</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,34 +2077,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>697022</v>
+        <v>697008</v>
       </c>
       <c r="R15" t="n">
-        <v>7323625</v>
+        <v>7323621</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2145,18 +2145,19 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2167,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118682711</v>
+        <v>118682713</v>
       </c>
       <c r="B16" t="n">
-        <v>78129</v>
+        <v>91779</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,25 +2180,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2207,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>697022</v>
+        <v>696803</v>
       </c>
       <c r="R16" t="n">
-        <v>7323626</v>
+        <v>7323628</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118683804</v>
+        <v>118671533</v>
       </c>
       <c r="B17" t="n">
-        <v>78129</v>
+        <v>89906</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2285,41 +2286,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>5685</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696768</v>
+        <v>696845</v>
       </c>
       <c r="R17" t="n">
-        <v>7323612</v>
+        <v>7323632</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2363,12 +2364,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2379,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118683827</v>
+        <v>118683799</v>
       </c>
       <c r="B18" t="n">
-        <v>77868</v>
+        <v>78129</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2395,21 +2396,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2419,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696832</v>
+        <v>697022</v>
       </c>
       <c r="R18" t="n">
-        <v>7323578</v>
+        <v>7323625</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2485,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118683826</v>
+        <v>118682711</v>
       </c>
       <c r="B19" t="n">
-        <v>77868</v>
+        <v>78129</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2501,37 +2502,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696900</v>
+        <v>697022</v>
       </c>
       <c r="R19" t="n">
-        <v>7323650</v>
+        <v>7323626</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2575,12 +2576,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2591,10 +2592,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118684523</v>
+        <v>118683804</v>
       </c>
       <c r="B20" t="n">
-        <v>77868</v>
+        <v>78129</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,37 +2608,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696848</v>
+        <v>696768</v>
       </c>
       <c r="R20" t="n">
-        <v>7323640</v>
+        <v>7323612</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2681,12 +2682,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2697,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118683022</v>
+        <v>118683758</v>
       </c>
       <c r="B21" t="n">
-        <v>77868</v>
+        <v>79102</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2713,34 +2714,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697008</v>
+        <v>696843</v>
       </c>
       <c r="R21" t="n">
-        <v>7323621</v>
+        <v>7323526</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2781,19 +2782,18 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3229,7 +3229,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118684516</v>
+        <v>118683768</v>
       </c>
       <c r="B26" t="n">
         <v>79102</v>
@@ -3265,17 +3265,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>697059</v>
+        <v>696728</v>
       </c>
       <c r="R26" t="n">
-        <v>7323655</v>
+        <v>7323627</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3319,12 +3319,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118682766</v>
+        <v>118682935</v>
       </c>
       <c r="B27" t="n">
-        <v>79102</v>
+        <v>91779</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3347,41 +3347,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696993</v>
+        <v>696866</v>
       </c>
       <c r="R27" t="n">
-        <v>7323679</v>
+        <v>7323727</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3425,12 +3425,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3441,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118673276</v>
+        <v>118682816</v>
       </c>
       <c r="B28" t="n">
-        <v>90666</v>
+        <v>91779</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3453,41 +3453,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1588</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696724</v>
+        <v>696806</v>
       </c>
       <c r="R28" t="n">
-        <v>7323610</v>
+        <v>7323536</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3531,12 +3531,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3547,10 +3547,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118682935</v>
+        <v>118684516</v>
       </c>
       <c r="B29" t="n">
-        <v>91779</v>
+        <v>79102</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3559,38 +3559,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696866</v>
+        <v>697059</v>
       </c>
       <c r="R29" t="n">
-        <v>7323727</v>
+        <v>7323655</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3637,12 +3637,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3653,10 +3653,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118682705</v>
+        <v>118682766</v>
       </c>
       <c r="B30" t="n">
-        <v>90847</v>
+        <v>79102</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3665,41 +3665,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2062</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696960</v>
+        <v>696993</v>
       </c>
       <c r="R30" t="n">
-        <v>7323635</v>
+        <v>7323679</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3743,12 +3743,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3759,10 +3759,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118682816</v>
+        <v>118673276</v>
       </c>
       <c r="B31" t="n">
-        <v>91779</v>
+        <v>90666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3771,41 +3771,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>1588</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Anna-Lisabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696806</v>
+        <v>696724</v>
       </c>
       <c r="R31" t="n">
-        <v>7323536</v>
+        <v>7323610</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3849,12 +3849,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3865,10 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118683768</v>
+        <v>118682705</v>
       </c>
       <c r="B32" t="n">
-        <v>79102</v>
+        <v>90847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3877,41 +3877,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696728</v>
+        <v>696960</v>
       </c>
       <c r="R32" t="n">
-        <v>7323627</v>
+        <v>7323635</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3955,12 +3955,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -9171,10 +9171,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118683802</v>
+        <v>118683761</v>
       </c>
       <c r="B82" t="n">
-        <v>78129</v>
+        <v>79102</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9187,21 +9187,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9211,10 +9211,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>696995</v>
+        <v>697007</v>
       </c>
       <c r="R82" t="n">
-        <v>7323745</v>
+        <v>7323538</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9277,10 +9277,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118683020</v>
+        <v>118682773</v>
       </c>
       <c r="B83" t="n">
-        <v>91773</v>
+        <v>91969</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9293,34 +9293,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>696836</v>
+        <v>697008</v>
       </c>
       <c r="R83" t="n">
-        <v>7323512</v>
+        <v>7323675</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9361,18 +9361,19 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9383,10 +9384,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118686847</v>
+        <v>118683802</v>
       </c>
       <c r="B84" t="n">
-        <v>91779</v>
+        <v>78129</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9395,41 +9396,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>696928</v>
+        <v>696995</v>
       </c>
       <c r="R84" t="n">
-        <v>7323571</v>
+        <v>7323745</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9473,12 +9474,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9489,10 +9490,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118682773</v>
+        <v>118682776</v>
       </c>
       <c r="B85" t="n">
-        <v>91969</v>
+        <v>77868</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9505,21 +9506,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9529,10 +9530,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>697008</v>
+        <v>696978</v>
       </c>
       <c r="R85" t="n">
-        <v>7323675</v>
+        <v>7323682</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9596,7 +9597,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118682776</v>
+        <v>118683818</v>
       </c>
       <c r="B86" t="n">
         <v>77868</v>
@@ -9632,14 +9633,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>696978</v>
+        <v>697096</v>
       </c>
       <c r="R86" t="n">
-        <v>7323682</v>
+        <v>7323681</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9680,19 +9681,18 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9703,10 +9703,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118683818</v>
+        <v>118683020</v>
       </c>
       <c r="B87" t="n">
-        <v>77868</v>
+        <v>91773</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9719,34 +9719,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6437</v>
+        <v>4362</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>697096</v>
+        <v>696836</v>
       </c>
       <c r="R87" t="n">
-        <v>7323681</v>
+        <v>7323512</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9793,12 +9793,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9809,10 +9809,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118683761</v>
+        <v>118686847</v>
       </c>
       <c r="B88" t="n">
-        <v>79102</v>
+        <v>91779</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9821,41 +9821,41 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>697007</v>
+        <v>696928</v>
       </c>
       <c r="R88" t="n">
-        <v>7323538</v>
+        <v>7323571</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9899,12 +9899,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -12785,10 +12785,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118682824</v>
+        <v>118682922</v>
       </c>
       <c r="B116" t="n">
-        <v>77868</v>
+        <v>58133</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12797,41 +12797,41 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6437</v>
+        <v>208249</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>696977</v>
+        <v>696748</v>
       </c>
       <c r="R116" t="n">
-        <v>7323784</v>
+        <v>7323651</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12875,12 +12875,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12891,7 +12891,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118682944</v>
+        <v>118682824</v>
       </c>
       <c r="B117" t="n">
         <v>77868</v>
@@ -12927,17 +12927,17 @@
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>696872</v>
+        <v>696977</v>
       </c>
       <c r="R117" t="n">
-        <v>7323693</v>
+        <v>7323784</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12981,12 +12981,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12997,7 +12997,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118670883</v>
+        <v>118682944</v>
       </c>
       <c r="B118" t="n">
         <v>77868</v>
@@ -13033,14 +13033,14 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>696727</v>
+        <v>696872</v>
       </c>
       <c r="R118" t="n">
-        <v>7323657</v>
+        <v>7323693</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13087,12 +13087,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -13103,10 +13103,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118682770</v>
+        <v>118670883</v>
       </c>
       <c r="B119" t="n">
-        <v>79102</v>
+        <v>77868</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13119,37 +13119,37 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>696742</v>
+        <v>696727</v>
       </c>
       <c r="R119" t="n">
-        <v>7323602</v>
+        <v>7323657</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13193,12 +13193,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -13209,7 +13209,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118682693</v>
+        <v>118682770</v>
       </c>
       <c r="B120" t="n">
         <v>79102</v>
@@ -13245,17 +13245,17 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>696755</v>
+        <v>696742</v>
       </c>
       <c r="R120" t="n">
-        <v>7323658</v>
+        <v>7323602</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13299,12 +13299,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13315,10 +13315,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118682696</v>
+        <v>118682693</v>
       </c>
       <c r="B121" t="n">
-        <v>90504</v>
+        <v>79102</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13331,21 +13331,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>696841</v>
+        <v>696755</v>
       </c>
       <c r="R121" t="n">
-        <v>7323553</v>
+        <v>7323658</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13421,10 +13421,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118671603</v>
+        <v>118682699</v>
       </c>
       <c r="B122" t="n">
-        <v>90654</v>
+        <v>91783</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13437,34 +13437,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1503</v>
+        <v>4365</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>696861</v>
+        <v>696914</v>
       </c>
       <c r="R122" t="n">
-        <v>7323661</v>
+        <v>7323653</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13511,22 +13511,26 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY122" t="inlineStr"/>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118682922</v>
+        <v>118682938</v>
       </c>
       <c r="B123" t="n">
-        <v>58133</v>
+        <v>91779</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13539,21 +13543,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>208249</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13563,10 +13567,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>696748</v>
+        <v>696826</v>
       </c>
       <c r="R123" t="n">
-        <v>7323651</v>
+        <v>7323664</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13629,10 +13633,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118682699</v>
+        <v>118682696</v>
       </c>
       <c r="B124" t="n">
-        <v>91783</v>
+        <v>90504</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13641,25 +13645,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4365</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13669,10 +13673,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>696914</v>
+        <v>696841</v>
       </c>
       <c r="R124" t="n">
-        <v>7323653</v>
+        <v>7323553</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13735,10 +13739,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118682938</v>
+        <v>118671603</v>
       </c>
       <c r="B125" t="n">
-        <v>91779</v>
+        <v>90654</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13747,38 +13751,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>696826</v>
+        <v>696861</v>
       </c>
       <c r="R125" t="n">
-        <v>7323664</v>
+        <v>7323661</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13825,26 +13829,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118682710</v>
+        <v>118683781</v>
       </c>
       <c r="B126" t="n">
-        <v>90749</v>
+        <v>79073</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13853,41 +13853,41 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>696760</v>
+        <v>696838</v>
       </c>
       <c r="R126" t="n">
-        <v>7323632</v>
+        <v>7323602</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13931,12 +13931,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13947,10 +13947,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118683760</v>
+        <v>118683780</v>
       </c>
       <c r="B127" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13963,21 +13963,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13987,10 +13987,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>696860</v>
+        <v>696853</v>
       </c>
       <c r="R127" t="n">
-        <v>7323545</v>
+        <v>7323635</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -14053,10 +14053,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118672765</v>
+        <v>118683785</v>
       </c>
       <c r="B128" t="n">
-        <v>90654</v>
+        <v>96807</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14065,41 +14065,41 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>697015</v>
+        <v>696899</v>
       </c>
       <c r="R128" t="n">
-        <v>7323529</v>
+        <v>7323655</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14143,12 +14143,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -14159,10 +14159,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118682712</v>
+        <v>118672765</v>
       </c>
       <c r="B129" t="n">
-        <v>91779</v>
+        <v>90654</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14171,38 +14171,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>697018</v>
+        <v>697015</v>
       </c>
       <c r="R129" t="n">
-        <v>7323682</v>
+        <v>7323529</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14249,12 +14249,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14265,10 +14265,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118683781</v>
+        <v>118682712</v>
       </c>
       <c r="B130" t="n">
-        <v>79073</v>
+        <v>91779</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14277,41 +14277,41 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>696838</v>
+        <v>697018</v>
       </c>
       <c r="R130" t="n">
-        <v>7323602</v>
+        <v>7323682</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14355,12 +14355,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14371,10 +14371,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118683780</v>
+        <v>118682710</v>
       </c>
       <c r="B131" t="n">
-        <v>79073</v>
+        <v>90749</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14383,41 +14383,41 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>696853</v>
+        <v>696760</v>
       </c>
       <c r="R131" t="n">
-        <v>7323635</v>
+        <v>7323632</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14461,12 +14461,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14477,10 +14477,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118683785</v>
+        <v>118683760</v>
       </c>
       <c r="B132" t="n">
-        <v>96807</v>
+        <v>79102</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14489,25 +14489,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14517,10 +14517,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>696899</v>
+        <v>696860</v>
       </c>
       <c r="R132" t="n">
-        <v>7323655</v>
+        <v>7323545</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -16809,10 +16809,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118682820</v>
+        <v>118683795</v>
       </c>
       <c r="B154" t="n">
-        <v>91779</v>
+        <v>77416</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16821,38 +16821,38 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>696817</v>
+        <v>697023</v>
       </c>
       <c r="R154" t="n">
-        <v>7323624</v>
+        <v>7323770</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -16893,18 +16893,19 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -16915,10 +16916,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118682918</v>
+        <v>118682708</v>
       </c>
       <c r="B155" t="n">
-        <v>79102</v>
+        <v>90654</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16927,25 +16928,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16955,10 +16956,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>696716</v>
+        <v>696767</v>
       </c>
       <c r="R155" t="n">
-        <v>7323623</v>
+        <v>7323634</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17005,12 +17006,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -17021,10 +17022,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>118682809</v>
+        <v>118683023</v>
       </c>
       <c r="B156" t="n">
-        <v>79102</v>
+        <v>77868</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17037,34 +17038,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>696817</v>
+        <v>697097</v>
       </c>
       <c r="R156" t="n">
-        <v>7323624</v>
+        <v>7323675</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -17105,18 +17106,19 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -17127,10 +17129,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118683765</v>
+        <v>118686850</v>
       </c>
       <c r="B157" t="n">
-        <v>79102</v>
+        <v>77868</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17143,37 +17145,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>696852</v>
+        <v>696841</v>
       </c>
       <c r="R157" t="n">
-        <v>7323640</v>
+        <v>7323544</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17217,12 +17219,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -17233,10 +17235,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118683766</v>
+        <v>118682820</v>
       </c>
       <c r="B158" t="n">
-        <v>79102</v>
+        <v>91779</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17245,38 +17247,38 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>696784</v>
+        <v>696817</v>
       </c>
       <c r="R158" t="n">
-        <v>7323649</v>
+        <v>7323624</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -17323,12 +17325,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -17339,10 +17341,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118682708</v>
+        <v>118682918</v>
       </c>
       <c r="B159" t="n">
-        <v>90654</v>
+        <v>79102</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17351,25 +17353,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17379,10 +17381,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>696767</v>
+        <v>696716</v>
       </c>
       <c r="R159" t="n">
-        <v>7323634</v>
+        <v>7323623</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17429,12 +17431,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -17445,10 +17447,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>118683777</v>
+        <v>118682809</v>
       </c>
       <c r="B160" t="n">
-        <v>79073</v>
+        <v>79102</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17461,34 +17463,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>697010</v>
+        <v>696817</v>
       </c>
       <c r="R160" t="n">
-        <v>7323702</v>
+        <v>7323624</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -17535,12 +17537,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -17551,10 +17553,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>118683023</v>
+        <v>118683765</v>
       </c>
       <c r="B161" t="n">
-        <v>77868</v>
+        <v>79102</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17567,34 +17569,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>697097</v>
+        <v>696852</v>
       </c>
       <c r="R161" t="n">
-        <v>7323675</v>
+        <v>7323640</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -17635,19 +17637,18 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -17658,10 +17659,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>118686850</v>
+        <v>118683766</v>
       </c>
       <c r="B162" t="n">
-        <v>77868</v>
+        <v>79102</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17674,37 +17675,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>696841</v>
+        <v>696784</v>
       </c>
       <c r="R162" t="n">
-        <v>7323544</v>
+        <v>7323649</v>
       </c>
       <c r="S162" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17748,12 +17749,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -17764,10 +17765,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>118683795</v>
+        <v>118683777</v>
       </c>
       <c r="B163" t="n">
-        <v>77416</v>
+        <v>79073</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17780,21 +17781,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17804,10 +17805,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>697023</v>
+        <v>697010</v>
       </c>
       <c r="R163" t="n">
-        <v>7323770</v>
+        <v>7323702</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -17848,7 +17849,6 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -18189,10 +18189,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>118682692</v>
+        <v>118672428</v>
       </c>
       <c r="B167" t="n">
-        <v>90469</v>
+        <v>91779</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18205,34 +18205,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>696974</v>
+        <v>697138</v>
       </c>
       <c r="R167" t="n">
-        <v>7323636</v>
+        <v>7323696</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18279,12 +18279,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -18295,10 +18295,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>118683007</v>
+        <v>118682765</v>
       </c>
       <c r="B168" t="n">
-        <v>79073</v>
+        <v>90469</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18307,38 +18307,38 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>697013</v>
+        <v>697012</v>
       </c>
       <c r="R168" t="n">
-        <v>7323628</v>
+        <v>7323651</v>
       </c>
       <c r="S168" t="n">
         <v>15</v>
@@ -18379,19 +18379,18 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -18402,10 +18401,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>118682930</v>
+        <v>118682692</v>
       </c>
       <c r="B169" t="n">
-        <v>90749</v>
+        <v>90469</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18414,25 +18413,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>65</v>
+        <v>5447</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18442,10 +18441,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>696846</v>
+        <v>696974</v>
       </c>
       <c r="R169" t="n">
-        <v>7323664</v>
+        <v>7323636</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18492,12 +18491,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -18508,10 +18507,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>118683800</v>
+        <v>118683007</v>
       </c>
       <c r="B170" t="n">
-        <v>78129</v>
+        <v>79073</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18524,34 +18523,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>697097</v>
+        <v>697013</v>
       </c>
       <c r="R170" t="n">
-        <v>7323699</v>
+        <v>7323628</v>
       </c>
       <c r="S170" t="n">
         <v>15</v>
@@ -18592,18 +18591,19 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -18614,10 +18614,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>118683004</v>
+        <v>118682930</v>
       </c>
       <c r="B171" t="n">
-        <v>79102</v>
+        <v>90749</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18626,41 +18626,41 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>696832</v>
+        <v>696846</v>
       </c>
       <c r="R171" t="n">
-        <v>7323503</v>
+        <v>7323664</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18704,12 +18704,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -18720,10 +18720,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>118672428</v>
+        <v>118683800</v>
       </c>
       <c r="B172" t="n">
-        <v>91779</v>
+        <v>78129</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18732,41 +18732,41 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>697138</v>
+        <v>697097</v>
       </c>
       <c r="R172" t="n">
-        <v>7323696</v>
+        <v>7323699</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18810,12 +18810,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -18826,10 +18826,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>118682765</v>
+        <v>118683004</v>
       </c>
       <c r="B173" t="n">
-        <v>90469</v>
+        <v>79102</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18838,38 +18838,38 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>697012</v>
+        <v>696832</v>
       </c>
       <c r="R173" t="n">
-        <v>7323651</v>
+        <v>7323503</v>
       </c>
       <c r="S173" t="n">
         <v>15</v>
@@ -18916,12 +18916,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -19676,10 +19676,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>118683831</v>
+        <v>118683797</v>
       </c>
       <c r="B181" t="n">
-        <v>77868</v>
+        <v>78129</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19692,21 +19692,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19716,10 +19716,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>696737</v>
+        <v>696843</v>
       </c>
       <c r="R181" t="n">
-        <v>7323611</v>
+        <v>7323526</v>
       </c>
       <c r="S181" t="n">
         <v>15</v>
@@ -19782,10 +19782,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>118683813</v>
+        <v>118684519</v>
       </c>
       <c r="B182" t="n">
-        <v>77868</v>
+        <v>78129</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19798,37 +19798,37 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>696906</v>
+        <v>696899</v>
       </c>
       <c r="R182" t="n">
-        <v>7323534</v>
+        <v>7323492</v>
       </c>
       <c r="S182" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19872,12 +19872,12 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -19888,10 +19888,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>118682916</v>
+        <v>118683831</v>
       </c>
       <c r="B183" t="n">
-        <v>79102</v>
+        <v>77868</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19904,37 +19904,37 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>696773</v>
+        <v>696737</v>
       </c>
       <c r="R183" t="n">
-        <v>7323660</v>
+        <v>7323611</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -19978,12 +19978,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -19994,10 +19994,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>118673032</v>
+        <v>118683813</v>
       </c>
       <c r="B184" t="n">
-        <v>90524</v>
+        <v>77868</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20010,37 +20010,37 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5442</v>
+        <v>6437</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>696724</v>
+        <v>696906</v>
       </c>
       <c r="R184" t="n">
-        <v>7323610</v>
+        <v>7323534</v>
       </c>
       <c r="S184" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -20084,12 +20084,12 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
@@ -20100,10 +20100,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>118683008</v>
+        <v>118682916</v>
       </c>
       <c r="B185" t="n">
-        <v>79073</v>
+        <v>79102</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20116,37 +20116,37 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>697097</v>
+        <v>696773</v>
       </c>
       <c r="R185" t="n">
-        <v>7323675</v>
+        <v>7323660</v>
       </c>
       <c r="S185" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -20184,19 +20184,18 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
@@ -20207,10 +20206,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>118683797</v>
+        <v>118683018</v>
       </c>
       <c r="B186" t="n">
-        <v>78129</v>
+        <v>77416</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20223,34 +20222,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>696843</v>
+        <v>697057</v>
       </c>
       <c r="R186" t="n">
-        <v>7323526</v>
+        <v>7323625</v>
       </c>
       <c r="S186" t="n">
         <v>15</v>
@@ -20297,12 +20296,12 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
@@ -20313,10 +20312,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>118684519</v>
+        <v>118682707</v>
       </c>
       <c r="B187" t="n">
-        <v>78129</v>
+        <v>90654</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20325,38 +20324,38 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>696899</v>
+        <v>697009</v>
       </c>
       <c r="R187" t="n">
-        <v>7323492</v>
+        <v>7323631</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20403,12 +20402,12 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -20419,10 +20418,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>118683018</v>
+        <v>118673032</v>
       </c>
       <c r="B188" t="n">
-        <v>77416</v>
+        <v>90524</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20435,37 +20434,37 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6487</v>
+        <v>5442</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Anna-Lisabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>697057</v>
+        <v>696724</v>
       </c>
       <c r="R188" t="n">
-        <v>7323625</v>
+        <v>7323610</v>
       </c>
       <c r="S188" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20509,12 +20508,12 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
@@ -20525,10 +20524,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>118682707</v>
+        <v>118682694</v>
       </c>
       <c r="B189" t="n">
-        <v>90654</v>
+        <v>90504</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20537,25 +20536,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1503</v>
+        <v>1202</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20565,10 +20564,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>697009</v>
+        <v>696806</v>
       </c>
       <c r="R189" t="n">
-        <v>7323631</v>
+        <v>7323628</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20631,10 +20630,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>118682694</v>
+        <v>118684517</v>
       </c>
       <c r="B190" t="n">
-        <v>90504</v>
+        <v>56502</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20643,38 +20642,38 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>696806</v>
+        <v>697021</v>
       </c>
       <c r="R190" t="n">
-        <v>7323628</v>
+        <v>7323671</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20721,12 +20720,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -20737,10 +20736,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>118684517</v>
+        <v>118683008</v>
       </c>
       <c r="B191" t="n">
-        <v>56502</v>
+        <v>79073</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20749,41 +20748,41 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>697021</v>
+        <v>697097</v>
       </c>
       <c r="R191" t="n">
-        <v>7323671</v>
+        <v>7323675</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20821,18 +20820,19 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
+      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -20843,10 +20843,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>118683025</v>
+        <v>118683762</v>
       </c>
       <c r="B192" t="n">
-        <v>77868</v>
+        <v>79102</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20859,34 +20859,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>696939</v>
+        <v>697090</v>
       </c>
       <c r="R192" t="n">
-        <v>7323649</v>
+        <v>7323699</v>
       </c>
       <c r="S192" t="n">
         <v>15</v>
@@ -20927,19 +20927,18 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -20950,10 +20949,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>118683030</v>
+        <v>118683783</v>
       </c>
       <c r="B193" t="n">
-        <v>77868</v>
+        <v>80441</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20966,34 +20965,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6437</v>
+        <v>1049</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>696777</v>
+        <v>696830</v>
       </c>
       <c r="R193" t="n">
-        <v>7323646</v>
+        <v>7323581</v>
       </c>
       <c r="S193" t="n">
         <v>15</v>
@@ -21034,19 +21033,18 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -21057,7 +21055,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>118682945</v>
+        <v>118683025</v>
       </c>
       <c r="B194" t="n">
         <v>77868</v>
@@ -21093,17 +21091,17 @@
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>696772</v>
+        <v>696939</v>
       </c>
       <c r="R194" t="n">
-        <v>7323668</v>
+        <v>7323649</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -21141,18 +21139,19 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -21163,7 +21162,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>118683029</v>
+        <v>118683030</v>
       </c>
       <c r="B195" t="n">
         <v>77868</v>
@@ -21203,10 +21202,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>696813</v>
+        <v>696777</v>
       </c>
       <c r="R195" t="n">
-        <v>7323676</v>
+        <v>7323646</v>
       </c>
       <c r="S195" t="n">
         <v>15</v>
@@ -21270,7 +21269,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>118682946</v>
+        <v>118682945</v>
       </c>
       <c r="B196" t="n">
         <v>77868</v>
@@ -21310,10 +21309,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>696744</v>
+        <v>696772</v>
       </c>
       <c r="R196" t="n">
-        <v>7323643</v>
+        <v>7323668</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21376,10 +21375,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>118683762</v>
+        <v>118683029</v>
       </c>
       <c r="B197" t="n">
-        <v>79102</v>
+        <v>77868</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21392,34 +21391,34 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>697090</v>
+        <v>696813</v>
       </c>
       <c r="R197" t="n">
-        <v>7323699</v>
+        <v>7323676</v>
       </c>
       <c r="S197" t="n">
         <v>15</v>
@@ -21460,18 +21459,19 @@
       <c r="AE197" t="b">
         <v>0</v>
       </c>
+      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -21482,10 +21482,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>118683012</v>
+        <v>118682946</v>
       </c>
       <c r="B198" t="n">
-        <v>96807</v>
+        <v>77868</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21494,41 +21494,41 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>221941</v>
+        <v>6437</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>696956</v>
+        <v>696744</v>
       </c>
       <c r="R198" t="n">
-        <v>7323675</v>
+        <v>7323643</v>
       </c>
       <c r="S198" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21572,12 +21572,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -21588,10 +21588,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>118682921</v>
+        <v>118682811</v>
       </c>
       <c r="B199" t="n">
-        <v>79073</v>
+        <v>90654</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21600,41 +21600,41 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>696716</v>
+        <v>696831</v>
       </c>
       <c r="R199" t="n">
-        <v>7323625</v>
+        <v>7323613</v>
       </c>
       <c r="S199" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21678,12 +21678,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -21694,10 +21694,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>118683783</v>
+        <v>118672352</v>
       </c>
       <c r="B200" t="n">
-        <v>80441</v>
+        <v>90654</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21706,41 +21706,41 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1049</v>
+        <v>1503</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>696830</v>
+        <v>697076</v>
       </c>
       <c r="R200" t="n">
-        <v>7323581</v>
+        <v>7323632</v>
       </c>
       <c r="S200" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -21784,12 +21784,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -21800,10 +21800,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>118682811</v>
+        <v>118682921</v>
       </c>
       <c r="B201" t="n">
-        <v>90654</v>
+        <v>79073</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21812,41 +21812,41 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>696831</v>
+        <v>696716</v>
       </c>
       <c r="R201" t="n">
-        <v>7323613</v>
+        <v>7323625</v>
       </c>
       <c r="S201" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21890,12 +21890,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -21906,10 +21906,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>118672352</v>
+        <v>118683012</v>
       </c>
       <c r="B202" t="n">
-        <v>90654</v>
+        <v>96807</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21918,41 +21918,41 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>697076</v>
+        <v>696956</v>
       </c>
       <c r="R202" t="n">
-        <v>7323632</v>
+        <v>7323675</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21996,12 +21996,12 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118683761</v>
+        <v>118673032</v>
       </c>
       <c r="B12" t="n">
-        <v>79109</v>
+        <v>90531</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,37 +1759,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>697007</v>
+        <v>696724</v>
       </c>
       <c r="R12" t="n">
-        <v>7323538</v>
+        <v>7323610</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1833,12 +1833,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1849,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118682709</v>
+        <v>118683826</v>
       </c>
       <c r="B13" t="n">
-        <v>90756</v>
+        <v>77875</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,41 +1861,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>697009</v>
+        <v>696900</v>
       </c>
       <c r="R13" t="n">
-        <v>7323631</v>
+        <v>7323650</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1939,12 +1939,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1955,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118673032</v>
+        <v>118686851</v>
       </c>
       <c r="B14" t="n">
-        <v>90531</v>
+        <v>77875</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1971,37 +1971,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696724</v>
+        <v>696925</v>
       </c>
       <c r="R14" t="n">
-        <v>7323610</v>
+        <v>7323592</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2045,12 +2045,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2061,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118683826</v>
+        <v>118683809</v>
       </c>
       <c r="B15" t="n">
         <v>77875</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696900</v>
+        <v>696804</v>
       </c>
       <c r="R15" t="n">
-        <v>7323650</v>
+        <v>7323510</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2167,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118686851</v>
+        <v>118683761</v>
       </c>
       <c r="B16" t="n">
-        <v>77875</v>
+        <v>79109</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,37 +2183,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696925</v>
+        <v>697007</v>
       </c>
       <c r="R16" t="n">
-        <v>7323592</v>
+        <v>7323538</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2257,12 +2257,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2273,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118683809</v>
+        <v>118683775</v>
       </c>
       <c r="B17" t="n">
-        <v>77875</v>
+        <v>79080</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,21 +2289,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696804</v>
+        <v>697098</v>
       </c>
       <c r="R17" t="n">
-        <v>7323510</v>
+        <v>7323697</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118682937</v>
+        <v>118683785</v>
       </c>
       <c r="B18" t="n">
-        <v>91786</v>
+        <v>96814</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2395,37 +2395,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696834</v>
+        <v>696899</v>
       </c>
       <c r="R18" t="n">
-        <v>7323670</v>
+        <v>7323655</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2469,12 +2469,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2485,10 +2485,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118682942</v>
+        <v>118682709</v>
       </c>
       <c r="B19" t="n">
-        <v>91780</v>
+        <v>90756</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2497,25 +2497,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>65</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696846</v>
+        <v>697009</v>
       </c>
       <c r="R19" t="n">
-        <v>7323660</v>
+        <v>7323631</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2575,12 +2575,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118683785</v>
+        <v>118682937</v>
       </c>
       <c r="B20" t="n">
-        <v>96814</v>
+        <v>91786</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2607,37 +2607,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696899</v>
+        <v>696834</v>
       </c>
       <c r="R20" t="n">
-        <v>7323655</v>
+        <v>7323670</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2681,12 +2681,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2697,10 +2697,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118683775</v>
+        <v>118682942</v>
       </c>
       <c r="B21" t="n">
-        <v>79080</v>
+        <v>91780</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2713,37 +2713,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>697098</v>
+        <v>696846</v>
       </c>
       <c r="R21" t="n">
-        <v>7323697</v>
+        <v>7323660</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2787,12 +2787,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118683766</v>
+        <v>118682774</v>
       </c>
       <c r="B22" t="n">
-        <v>79109</v>
+        <v>90661</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2815,38 +2815,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696784</v>
+        <v>697009</v>
       </c>
       <c r="R22" t="n">
-        <v>7323649</v>
+        <v>7323639</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2893,12 +2893,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2909,10 +2909,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118683764</v>
+        <v>118682771</v>
       </c>
       <c r="B23" t="n">
-        <v>79109</v>
+        <v>89582</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2925,34 +2925,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697005</v>
+        <v>697008</v>
       </c>
       <c r="R23" t="n">
-        <v>7323759</v>
+        <v>7323675</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2993,18 +2993,19 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3227,10 +3228,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118682938</v>
+        <v>118683766</v>
       </c>
       <c r="B26" t="n">
-        <v>91786</v>
+        <v>79109</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3239,41 +3240,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696826</v>
+        <v>696784</v>
       </c>
       <c r="R26" t="n">
-        <v>7323664</v>
+        <v>7323649</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3317,12 +3318,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3333,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118682774</v>
+        <v>118683764</v>
       </c>
       <c r="B27" t="n">
-        <v>90661</v>
+        <v>79109</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3345,38 +3346,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>697009</v>
+        <v>697005</v>
       </c>
       <c r="R27" t="n">
-        <v>7323639</v>
+        <v>7323759</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3423,12 +3424,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3439,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118682771</v>
+        <v>118682938</v>
       </c>
       <c r="B28" t="n">
-        <v>89582</v>
+        <v>91786</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,41 +3452,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>697008</v>
+        <v>696826</v>
       </c>
       <c r="R28" t="n">
-        <v>7323675</v>
+        <v>7323664</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3523,19 +3524,18 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -6201,10 +6201,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118671444</v>
+        <v>118683799</v>
       </c>
       <c r="B54" t="n">
-        <v>91786</v>
+        <v>78136</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6213,41 +6213,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696824</v>
+        <v>697022</v>
       </c>
       <c r="R54" t="n">
-        <v>7323626</v>
+        <v>7323625</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6291,12 +6291,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6307,10 +6307,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118673130</v>
+        <v>118682944</v>
       </c>
       <c r="B55" t="n">
-        <v>77423</v>
+        <v>77875</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6323,34 +6323,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696724</v>
+        <v>696872</v>
       </c>
       <c r="R55" t="n">
-        <v>7323610</v>
+        <v>7323693</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6397,12 +6397,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6413,7 +6413,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118682944</v>
+        <v>118670883</v>
       </c>
       <c r="B56" t="n">
         <v>77875</v>
@@ -6449,14 +6449,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696872</v>
+        <v>696727</v>
       </c>
       <c r="R56" t="n">
-        <v>7323693</v>
+        <v>7323657</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6503,12 +6503,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6519,10 +6519,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118670883</v>
+        <v>118671444</v>
       </c>
       <c r="B57" t="n">
-        <v>77875</v>
+        <v>91786</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6531,25 +6531,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696727</v>
+        <v>696824</v>
       </c>
       <c r="R57" t="n">
-        <v>7323657</v>
+        <v>7323626</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6731,10 +6731,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118683799</v>
+        <v>118673130</v>
       </c>
       <c r="B59" t="n">
-        <v>78136</v>
+        <v>77423</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6747,37 +6747,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>697022</v>
+        <v>696724</v>
       </c>
       <c r="R59" t="n">
-        <v>7323625</v>
+        <v>7323610</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6821,12 +6821,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -8323,7 +8323,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118683778</v>
+        <v>118682919</v>
       </c>
       <c r="B74" t="n">
         <v>79080</v>
@@ -8359,17 +8359,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696970</v>
+        <v>696875</v>
       </c>
       <c r="R74" t="n">
-        <v>7323681</v>
+        <v>7323766</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8413,12 +8413,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8429,7 +8429,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118682919</v>
+        <v>118683778</v>
       </c>
       <c r="B75" t="n">
         <v>79080</v>
@@ -8465,17 +8465,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696875</v>
+        <v>696970</v>
       </c>
       <c r="R75" t="n">
-        <v>7323766</v>
+        <v>7323681</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8519,12 +8519,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8535,10 +8535,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118682930</v>
+        <v>118682707</v>
       </c>
       <c r="B76" t="n">
-        <v>90756</v>
+        <v>90661</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8551,21 +8551,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>65</v>
+        <v>1503</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8575,10 +8575,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696846</v>
+        <v>697009</v>
       </c>
       <c r="R76" t="n">
-        <v>7323664</v>
+        <v>7323631</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8625,12 +8625,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8641,10 +8641,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118683808</v>
+        <v>118686843</v>
       </c>
       <c r="B77" t="n">
-        <v>77423</v>
+        <v>80448</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8657,37 +8657,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6487</v>
+        <v>1049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>696747</v>
+        <v>696934</v>
       </c>
       <c r="R77" t="n">
-        <v>7323606</v>
+        <v>7323591</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8731,12 +8731,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8747,7 +8747,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118686845</v>
+        <v>118683808</v>
       </c>
       <c r="B78" t="n">
         <v>77423</v>
@@ -8783,17 +8783,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696856</v>
+        <v>696747</v>
       </c>
       <c r="R78" t="n">
-        <v>7323627</v>
+        <v>7323606</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8837,12 +8837,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8853,7 +8853,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118683806</v>
+        <v>118686845</v>
       </c>
       <c r="B79" t="n">
         <v>77423</v>
@@ -8889,17 +8889,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696963</v>
+        <v>696856</v>
       </c>
       <c r="R79" t="n">
-        <v>7323687</v>
+        <v>7323627</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8943,12 +8943,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8959,7 +8959,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118683017</v>
+        <v>118683806</v>
       </c>
       <c r="B80" t="n">
         <v>77423</v>
@@ -8995,14 +8995,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>697052</v>
+        <v>696963</v>
       </c>
       <c r="R80" t="n">
-        <v>7323652</v>
+        <v>7323687</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9049,12 +9049,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -9065,10 +9065,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118683019</v>
+        <v>118682930</v>
       </c>
       <c r="B81" t="n">
-        <v>77423</v>
+        <v>90756</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9077,41 +9077,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6487</v>
+        <v>65</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>697090</v>
+        <v>696846</v>
       </c>
       <c r="R81" t="n">
-        <v>7323674</v>
+        <v>7323664</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9149,19 +9149,18 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9172,10 +9171,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118682707</v>
+        <v>118683017</v>
       </c>
       <c r="B82" t="n">
-        <v>90661</v>
+        <v>77423</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9184,41 +9183,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>697009</v>
+        <v>697052</v>
       </c>
       <c r="R82" t="n">
-        <v>7323631</v>
+        <v>7323652</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9262,12 +9261,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -9278,10 +9277,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118686843</v>
+        <v>118683019</v>
       </c>
       <c r="B83" t="n">
-        <v>80448</v>
+        <v>77423</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9294,37 +9293,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1049</v>
+        <v>6487</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>696934</v>
+        <v>697090</v>
       </c>
       <c r="R83" t="n">
-        <v>7323591</v>
+        <v>7323674</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9362,18 +9361,19 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -11081,10 +11081,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118683798</v>
+        <v>118684518</v>
       </c>
       <c r="B100" t="n">
-        <v>78136</v>
+        <v>96814</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11093,41 +11093,41 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>696908</v>
+        <v>696896</v>
       </c>
       <c r="R100" t="n">
-        <v>7323561</v>
+        <v>7323658</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11171,12 +11171,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11187,10 +11187,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118671603</v>
+        <v>118682926</v>
       </c>
       <c r="B101" t="n">
-        <v>90661</v>
+        <v>96814</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11199,38 +11199,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>696861</v>
+        <v>696967</v>
       </c>
       <c r="R101" t="n">
-        <v>7323661</v>
+        <v>7323736</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11277,22 +11277,26 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
+          <t>Julia Lea Falk, Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118682696</v>
+        <v>118683774</v>
       </c>
       <c r="B102" t="n">
-        <v>90511</v>
+        <v>79080</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11305,37 +11309,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>696841</v>
+        <v>697096</v>
       </c>
       <c r="R102" t="n">
-        <v>7323553</v>
+        <v>7323682</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11379,12 +11383,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11925,10 +11929,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118683783</v>
+        <v>118683798</v>
       </c>
       <c r="B108" t="n">
-        <v>80448</v>
+        <v>78136</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11941,21 +11945,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11965,10 +11969,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>696830</v>
+        <v>696908</v>
       </c>
       <c r="R108" t="n">
-        <v>7323581</v>
+        <v>7323561</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -12031,10 +12035,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118683774</v>
+        <v>118671603</v>
       </c>
       <c r="B109" t="n">
-        <v>79080</v>
+        <v>90661</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12043,41 +12047,41 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>697096</v>
+        <v>696861</v>
       </c>
       <c r="R109" t="n">
-        <v>7323682</v>
+        <v>7323661</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12121,26 +12125,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118684518</v>
+        <v>118682696</v>
       </c>
       <c r="B110" t="n">
-        <v>96814</v>
+        <v>90511</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12149,38 +12149,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>696896</v>
+        <v>696841</v>
       </c>
       <c r="R110" t="n">
-        <v>7323658</v>
+        <v>7323553</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12227,12 +12227,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -12243,10 +12243,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118682926</v>
+        <v>118683783</v>
       </c>
       <c r="B111" t="n">
-        <v>96814</v>
+        <v>80448</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12255,41 +12255,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221941</v>
+        <v>1049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>696967</v>
+        <v>696830</v>
       </c>
       <c r="R111" t="n">
-        <v>7323736</v>
+        <v>7323581</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12333,12 +12333,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12349,10 +12349,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118682776</v>
+        <v>118683800</v>
       </c>
       <c r="B112" t="n">
-        <v>77875</v>
+        <v>78136</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12365,34 +12365,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>696978</v>
+        <v>697097</v>
       </c>
       <c r="R112" t="n">
-        <v>7323682</v>
+        <v>7323699</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12433,19 +12433,18 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12456,10 +12455,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118683824</v>
+        <v>118682775</v>
       </c>
       <c r="B113" t="n">
-        <v>77875</v>
+        <v>90661</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12468,38 +12467,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>696905</v>
+        <v>696814</v>
       </c>
       <c r="R113" t="n">
-        <v>7323662</v>
+        <v>7323639</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -12546,12 +12545,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12562,10 +12561,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118682915</v>
+        <v>118682776</v>
       </c>
       <c r="B114" t="n">
-        <v>79109</v>
+        <v>77875</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12578,37 +12577,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>696914</v>
+        <v>696978</v>
       </c>
       <c r="R114" t="n">
-        <v>7323793</v>
+        <v>7323682</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12646,18 +12645,19 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12668,10 +12668,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118682766</v>
+        <v>118683824</v>
       </c>
       <c r="B115" t="n">
-        <v>79109</v>
+        <v>77875</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12684,34 +12684,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>696993</v>
+        <v>696905</v>
       </c>
       <c r="R115" t="n">
-        <v>7323679</v>
+        <v>7323662</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12758,12 +12758,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12774,10 +12774,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118683800</v>
+        <v>118682915</v>
       </c>
       <c r="B116" t="n">
-        <v>78136</v>
+        <v>79109</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12790,37 +12790,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>697097</v>
+        <v>696914</v>
       </c>
       <c r="R116" t="n">
-        <v>7323699</v>
+        <v>7323793</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12864,12 +12864,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12880,10 +12880,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118682775</v>
+        <v>118682766</v>
       </c>
       <c r="B117" t="n">
-        <v>90661</v>
+        <v>79109</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12892,25 +12892,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12920,10 +12920,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>696814</v>
+        <v>696993</v>
       </c>
       <c r="R117" t="n">
-        <v>7323639</v>
+        <v>7323679</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -14046,10 +14046,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118683802</v>
+        <v>118683031</v>
       </c>
       <c r="B128" t="n">
-        <v>78136</v>
+        <v>77875</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14062,34 +14062,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>696995</v>
+        <v>696746</v>
       </c>
       <c r="R128" t="n">
-        <v>7323745</v>
+        <v>7323620</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -14130,18 +14130,19 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -14152,10 +14153,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118682814</v>
+        <v>118683023</v>
       </c>
       <c r="B129" t="n">
-        <v>78136</v>
+        <v>77875</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14168,34 +14169,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>696890</v>
+        <v>697097</v>
       </c>
       <c r="R129" t="n">
-        <v>7323617</v>
+        <v>7323675</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -14236,18 +14237,19 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -14258,10 +14260,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118683031</v>
+        <v>118682699</v>
       </c>
       <c r="B130" t="n">
-        <v>77875</v>
+        <v>91790</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14270,41 +14272,41 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6437</v>
+        <v>4365</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>696746</v>
+        <v>696914</v>
       </c>
       <c r="R130" t="n">
-        <v>7323620</v>
+        <v>7323653</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14342,19 +14344,18 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14365,10 +14366,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118683023</v>
+        <v>118672140</v>
       </c>
       <c r="B131" t="n">
-        <v>77875</v>
+        <v>91786</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14377,41 +14378,41 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>697097</v>
+        <v>697004</v>
       </c>
       <c r="R131" t="n">
-        <v>7323675</v>
+        <v>7323588</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14449,19 +14450,18 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -14472,10 +14472,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118671533</v>
+        <v>118682820</v>
       </c>
       <c r="B132" t="n">
-        <v>89913</v>
+        <v>91786</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14488,37 +14488,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>696845</v>
+        <v>696817</v>
       </c>
       <c r="R132" t="n">
-        <v>7323632</v>
+        <v>7323624</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14562,12 +14562,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14578,10 +14578,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118682699</v>
+        <v>118682713</v>
       </c>
       <c r="B133" t="n">
-        <v>91790</v>
+        <v>91786</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14590,25 +14590,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14618,10 +14618,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>696914</v>
+        <v>696803</v>
       </c>
       <c r="R133" t="n">
-        <v>7323653</v>
+        <v>7323628</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14684,10 +14684,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118672140</v>
+        <v>118673080</v>
       </c>
       <c r="B134" t="n">
-        <v>91786</v>
+        <v>91780</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14696,38 +14696,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Anna-Lisabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>697004</v>
+        <v>696724</v>
       </c>
       <c r="R134" t="n">
-        <v>7323588</v>
+        <v>7323610</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14790,7 +14790,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118682820</v>
+        <v>118682932</v>
       </c>
       <c r="B135" t="n">
         <v>91786</v>
@@ -14826,17 +14826,17 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>696817</v>
+        <v>696873</v>
       </c>
       <c r="R135" t="n">
-        <v>7323624</v>
+        <v>7323783</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14880,12 +14880,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14896,10 +14896,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118682713</v>
+        <v>118683779</v>
       </c>
       <c r="B136" t="n">
-        <v>91786</v>
+        <v>79080</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14908,41 +14908,41 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>696803</v>
+        <v>696901</v>
       </c>
       <c r="R136" t="n">
-        <v>7323628</v>
+        <v>7323660</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14986,12 +14986,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -15002,10 +15002,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118673080</v>
+        <v>118683802</v>
       </c>
       <c r="B137" t="n">
-        <v>91780</v>
+        <v>78136</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15018,37 +15018,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>696724</v>
+        <v>696995</v>
       </c>
       <c r="R137" t="n">
-        <v>7323610</v>
+        <v>7323745</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15092,12 +15092,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -15108,10 +15108,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118682932</v>
+        <v>118682814</v>
       </c>
       <c r="B138" t="n">
-        <v>91786</v>
+        <v>78136</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15120,41 +15120,41 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>696873</v>
+        <v>696890</v>
       </c>
       <c r="R138" t="n">
-        <v>7323783</v>
+        <v>7323617</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15198,12 +15198,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -15214,10 +15214,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118683779</v>
+        <v>118671533</v>
       </c>
       <c r="B139" t="n">
-        <v>79080</v>
+        <v>89913</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15226,41 +15226,41 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>5685</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>696901</v>
+        <v>696845</v>
       </c>
       <c r="R139" t="n">
-        <v>7323660</v>
+        <v>7323632</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15304,12 +15304,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -15320,10 +15320,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118683791</v>
+        <v>118683008</v>
       </c>
       <c r="B140" t="n">
-        <v>80448</v>
+        <v>79080</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15336,34 +15336,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>696808</v>
+        <v>697097</v>
       </c>
       <c r="R140" t="n">
-        <v>7323509</v>
+        <v>7323675</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -15404,18 +15404,19 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15426,10 +15427,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118682710</v>
+        <v>118671198</v>
       </c>
       <c r="B141" t="n">
-        <v>90756</v>
+        <v>79080</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15438,38 +15439,38 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>696760</v>
+        <v>696727</v>
       </c>
       <c r="R141" t="n">
-        <v>7323632</v>
+        <v>7323649</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15516,12 +15517,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -15532,10 +15533,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118686848</v>
+        <v>118682710</v>
       </c>
       <c r="B142" t="n">
-        <v>77875</v>
+        <v>90756</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15544,41 +15545,41 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>696705</v>
+        <v>696760</v>
       </c>
       <c r="R142" t="n">
-        <v>7323661</v>
+        <v>7323632</v>
       </c>
       <c r="S142" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15622,12 +15623,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15638,10 +15639,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118683022</v>
+        <v>118671737</v>
       </c>
       <c r="B143" t="n">
-        <v>77875</v>
+        <v>91780</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15654,37 +15655,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6437</v>
+        <v>4362</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>697008</v>
+        <v>696905</v>
       </c>
       <c r="R143" t="n">
-        <v>7323621</v>
+        <v>7323645</v>
       </c>
       <c r="S143" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15722,19 +15723,18 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -15745,10 +15745,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118683008</v>
+        <v>118686848</v>
       </c>
       <c r="B144" t="n">
-        <v>79080</v>
+        <v>77875</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15761,37 +15761,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>697097</v>
+        <v>696705</v>
       </c>
       <c r="R144" t="n">
-        <v>7323675</v>
+        <v>7323661</v>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15829,19 +15829,18 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15852,10 +15851,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118671198</v>
+        <v>118683022</v>
       </c>
       <c r="B145" t="n">
-        <v>79080</v>
+        <v>77875</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15868,37 +15867,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>696727</v>
+        <v>697008</v>
       </c>
       <c r="R145" t="n">
-        <v>7323649</v>
+        <v>7323621</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15936,18 +15935,19 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15958,7 +15958,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118671958</v>
+        <v>118683018</v>
       </c>
       <c r="B146" t="n">
         <v>77423</v>
@@ -15994,17 +15994,17 @@
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>696938</v>
+        <v>697057</v>
       </c>
       <c r="R146" t="n">
-        <v>7323662</v>
+        <v>7323625</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16048,12 +16048,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -16064,10 +16064,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118672105</v>
+        <v>118683791</v>
       </c>
       <c r="B147" t="n">
-        <v>91780</v>
+        <v>80448</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16080,37 +16080,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4362</v>
+        <v>1049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>696962</v>
+        <v>696808</v>
       </c>
       <c r="R147" t="n">
-        <v>7323622</v>
+        <v>7323509</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16154,12 +16154,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -16170,10 +16170,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118686847</v>
+        <v>118672105</v>
       </c>
       <c r="B148" t="n">
-        <v>91786</v>
+        <v>91780</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16182,41 +16182,41 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>696928</v>
+        <v>696962</v>
       </c>
       <c r="R148" t="n">
-        <v>7323571</v>
+        <v>7323622</v>
       </c>
       <c r="S148" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16260,12 +16260,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -16276,7 +16276,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118682816</v>
+        <v>118686847</v>
       </c>
       <c r="B149" t="n">
         <v>91786</v>
@@ -16312,17 +16312,17 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>696806</v>
+        <v>696928</v>
       </c>
       <c r="R149" t="n">
-        <v>7323536</v>
+        <v>7323571</v>
       </c>
       <c r="S149" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16366,12 +16366,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -16382,10 +16382,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118671737</v>
+        <v>118682816</v>
       </c>
       <c r="B150" t="n">
-        <v>91780</v>
+        <v>91786</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16394,41 +16394,41 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>696905</v>
+        <v>696806</v>
       </c>
       <c r="R150" t="n">
-        <v>7323645</v>
+        <v>7323536</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16472,12 +16472,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -16488,7 +16488,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118683018</v>
+        <v>118671958</v>
       </c>
       <c r="B151" t="n">
         <v>77423</v>
@@ -16524,17 +16524,17 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>697057</v>
+        <v>696938</v>
       </c>
       <c r="R151" t="n">
-        <v>7323625</v>
+        <v>7323662</v>
       </c>
       <c r="S151" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16578,12 +16578,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -20518,7 +20518,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>118684516</v>
+        <v>118683760</v>
       </c>
       <c r="B189" t="n">
         <v>79109</v>
@@ -20554,17 +20554,17 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>697059</v>
+        <v>696860</v>
       </c>
       <c r="R189" t="n">
-        <v>7323655</v>
+        <v>7323545</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20608,12 +20608,12 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
@@ -20624,7 +20624,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>118683760</v>
+        <v>118682770</v>
       </c>
       <c r="B190" t="n">
         <v>79109</v>
@@ -20660,14 +20660,14 @@
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>696860</v>
+        <v>696742</v>
       </c>
       <c r="R190" t="n">
-        <v>7323545</v>
+        <v>7323602</v>
       </c>
       <c r="S190" t="n">
         <v>15</v>
@@ -20714,12 +20714,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -20730,10 +20730,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>118682770</v>
+        <v>118682935</v>
       </c>
       <c r="B191" t="n">
-        <v>79109</v>
+        <v>91786</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20742,41 +20742,41 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>696742</v>
+        <v>696866</v>
       </c>
       <c r="R191" t="n">
-        <v>7323602</v>
+        <v>7323727</v>
       </c>
       <c r="S191" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20820,12 +20820,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -20836,10 +20836,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>118683028</v>
+        <v>118684517</v>
       </c>
       <c r="B192" t="n">
-        <v>77875</v>
+        <v>56502</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20848,41 +20848,41 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6437</v>
+        <v>100138</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>696825</v>
+        <v>697021</v>
       </c>
       <c r="R192" t="n">
-        <v>7323668</v>
+        <v>7323671</v>
       </c>
       <c r="S192" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -20920,19 +20920,18 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -20943,10 +20942,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>118682935</v>
+        <v>118683007</v>
       </c>
       <c r="B193" t="n">
-        <v>91786</v>
+        <v>79080</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20955,41 +20954,41 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>696866</v>
+        <v>697013</v>
       </c>
       <c r="R193" t="n">
-        <v>7323727</v>
+        <v>7323628</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21027,18 +21026,19 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -21049,10 +21049,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>118684517</v>
+        <v>118683028</v>
       </c>
       <c r="B194" t="n">
-        <v>56502</v>
+        <v>77875</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21061,41 +21061,41 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>697021</v>
+        <v>696825</v>
       </c>
       <c r="R194" t="n">
-        <v>7323671</v>
+        <v>7323668</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -21133,18 +21133,19 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -21155,10 +21156,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>118683007</v>
+        <v>118684516</v>
       </c>
       <c r="B195" t="n">
-        <v>79080</v>
+        <v>79109</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21171,37 +21172,37 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>697013</v>
+        <v>697059</v>
       </c>
       <c r="R195" t="n">
-        <v>7323628</v>
+        <v>7323655</v>
       </c>
       <c r="S195" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -21239,19 +21240,18 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -21262,10 +21262,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>118682821</v>
+        <v>118683776</v>
       </c>
       <c r="B196" t="n">
-        <v>77875</v>
+        <v>79080</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21278,34 +21278,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>696870</v>
+        <v>697001</v>
       </c>
       <c r="R196" t="n">
-        <v>7323489</v>
+        <v>7323753</v>
       </c>
       <c r="S196" t="n">
         <v>15</v>
@@ -21352,12 +21352,12 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
@@ -21368,10 +21368,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>118683011</v>
+        <v>118686836</v>
       </c>
       <c r="B197" t="n">
-        <v>91790</v>
+        <v>79109</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21380,41 +21380,41 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>697000</v>
+        <v>696835</v>
       </c>
       <c r="R197" t="n">
-        <v>7323690</v>
+        <v>7323611</v>
       </c>
       <c r="S197" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21458,12 +21458,12 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -21474,10 +21474,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>118683014</v>
+        <v>118683011</v>
       </c>
       <c r="B198" t="n">
-        <v>91786</v>
+        <v>91790</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21486,25 +21486,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21514,10 +21514,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>697030</v>
+        <v>697000</v>
       </c>
       <c r="R198" t="n">
-        <v>7323694</v>
+        <v>7323690</v>
       </c>
       <c r="S198" t="n">
         <v>15</v>
@@ -21580,7 +21580,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>118682931</v>
+        <v>118683014</v>
       </c>
       <c r="B199" t="n">
         <v>91786</v>
@@ -21616,17 +21616,17 @@
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>697001</v>
+        <v>697030</v>
       </c>
       <c r="R199" t="n">
-        <v>7323764</v>
+        <v>7323694</v>
       </c>
       <c r="S199" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -21670,12 +21670,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -21686,7 +21686,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>118682712</v>
+        <v>118682931</v>
       </c>
       <c r="B200" t="n">
         <v>91786</v>
@@ -21726,10 +21726,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>697018</v>
+        <v>697001</v>
       </c>
       <c r="R200" t="n">
-        <v>7323682</v>
+        <v>7323764</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21776,12 +21776,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -21792,10 +21792,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>118686836</v>
+        <v>118682712</v>
       </c>
       <c r="B201" t="n">
-        <v>79109</v>
+        <v>91786</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21804,41 +21804,41 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>696835</v>
+        <v>697018</v>
       </c>
       <c r="R201" t="n">
-        <v>7323611</v>
+        <v>7323682</v>
       </c>
       <c r="S201" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21882,12 +21882,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -21898,10 +21898,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>118683004</v>
+        <v>118682708</v>
       </c>
       <c r="B202" t="n">
-        <v>79109</v>
+        <v>90661</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21910,41 +21910,41 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>696832</v>
+        <v>696767</v>
       </c>
       <c r="R202" t="n">
-        <v>7323503</v>
+        <v>7323634</v>
       </c>
       <c r="S202" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21988,12 +21988,12 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -22004,10 +22004,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>118683758</v>
+        <v>118682692</v>
       </c>
       <c r="B203" t="n">
-        <v>79109</v>
+        <v>90476</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22016,41 +22016,41 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>696843</v>
+        <v>696974</v>
       </c>
       <c r="R203" t="n">
-        <v>7323526</v>
+        <v>7323636</v>
       </c>
       <c r="S203" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22094,12 +22094,12 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
@@ -22110,10 +22110,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>118682810</v>
+        <v>118682821</v>
       </c>
       <c r="B204" t="n">
-        <v>77423</v>
+        <v>77875</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22126,21 +22126,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22150,10 +22150,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>697035</v>
+        <v>696870</v>
       </c>
       <c r="R204" t="n">
-        <v>7323488</v>
+        <v>7323489</v>
       </c>
       <c r="S204" t="n">
         <v>15</v>
@@ -22194,7 +22194,6 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
-      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
@@ -22217,10 +22216,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>118682772</v>
+        <v>118683004</v>
       </c>
       <c r="B205" t="n">
-        <v>56502</v>
+        <v>79109</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22229,46 +22228,38 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>697008</v>
+        <v>696832</v>
       </c>
       <c r="R205" t="n">
-        <v>7323675</v>
+        <v>7323503</v>
       </c>
       <c r="S205" t="n">
         <v>15</v>
@@ -22315,12 +22306,12 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
@@ -22331,10 +22322,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>118682708</v>
+        <v>118683758</v>
       </c>
       <c r="B206" t="n">
-        <v>90661</v>
+        <v>79109</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22343,41 +22334,41 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>696767</v>
+        <v>696843</v>
       </c>
       <c r="R206" t="n">
-        <v>7323634</v>
+        <v>7323526</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -22421,12 +22412,12 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
@@ -22437,10 +22428,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>118682692</v>
+        <v>118682810</v>
       </c>
       <c r="B207" t="n">
-        <v>90476</v>
+        <v>77423</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22449,41 +22440,41 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5447</v>
+        <v>6487</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>696974</v>
+        <v>697035</v>
       </c>
       <c r="R207" t="n">
-        <v>7323636</v>
+        <v>7323488</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -22521,18 +22512,19 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
+      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
@@ -22543,10 +22535,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>118683776</v>
+        <v>118682772</v>
       </c>
       <c r="B208" t="n">
-        <v>79080</v>
+        <v>56502</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -22555,38 +22547,46 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>697001</v>
+        <v>697008</v>
       </c>
       <c r="R208" t="n">
-        <v>7323753</v>
+        <v>7323675</v>
       </c>
       <c r="S208" t="n">
         <v>15</v>
@@ -22633,12 +22633,12 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
@@ -22649,10 +22649,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>118682811</v>
+        <v>118682928</v>
       </c>
       <c r="B209" t="n">
-        <v>90661</v>
+        <v>78227</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22661,41 +22661,41 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>696831</v>
+        <v>696717</v>
       </c>
       <c r="R209" t="n">
-        <v>7323613</v>
+        <v>7323620</v>
       </c>
       <c r="S209" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22739,12 +22739,12 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
@@ -22755,10 +22755,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>118683030</v>
+        <v>118672115</v>
       </c>
       <c r="B210" t="n">
-        <v>77875</v>
+        <v>78136</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22771,37 +22771,37 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>696777</v>
+        <v>697004</v>
       </c>
       <c r="R210" t="n">
-        <v>7323646</v>
+        <v>7323588</v>
       </c>
       <c r="S210" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -22839,19 +22839,18 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
@@ -22862,10 +22861,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>118686849</v>
+        <v>118682811</v>
       </c>
       <c r="B211" t="n">
-        <v>77875</v>
+        <v>90661</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22874,41 +22873,41 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>696823</v>
+        <v>696831</v>
       </c>
       <c r="R211" t="n">
-        <v>7323579</v>
+        <v>7323613</v>
       </c>
       <c r="S211" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -22952,12 +22951,12 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
@@ -22968,7 +22967,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>118683815</v>
+        <v>118683030</v>
       </c>
       <c r="B212" t="n">
         <v>77875</v>
@@ -23004,14 +23003,14 @@
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>697006</v>
+        <v>696777</v>
       </c>
       <c r="R212" t="n">
-        <v>7323539</v>
+        <v>7323646</v>
       </c>
       <c r="S212" t="n">
         <v>15</v>
@@ -23052,18 +23051,19 @@
       <c r="AE212" t="b">
         <v>0</v>
       </c>
+      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
@@ -23074,7 +23074,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>118683829</v>
+        <v>118686849</v>
       </c>
       <c r="B213" t="n">
         <v>77875</v>
@@ -23110,17 +23110,17 @@
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>696785</v>
+        <v>696823</v>
       </c>
       <c r="R213" t="n">
-        <v>7323647</v>
+        <v>7323579</v>
       </c>
       <c r="S213" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23164,12 +23164,12 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
@@ -23180,10 +23180,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>118682928</v>
+        <v>118683815</v>
       </c>
       <c r="B214" t="n">
-        <v>78227</v>
+        <v>77875</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23196,37 +23196,37 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>696717</v>
+        <v>697006</v>
       </c>
       <c r="R214" t="n">
-        <v>7323620</v>
+        <v>7323539</v>
       </c>
       <c r="S214" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -23270,12 +23270,12 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
@@ -23286,10 +23286,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>118683020</v>
+        <v>118683829</v>
       </c>
       <c r="B215" t="n">
-        <v>91780</v>
+        <v>77875</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -23302,34 +23302,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>696836</v>
+        <v>696785</v>
       </c>
       <c r="R215" t="n">
-        <v>7323512</v>
+        <v>7323647</v>
       </c>
       <c r="S215" t="n">
         <v>15</v>
@@ -23376,12 +23376,12 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
@@ -23392,10 +23392,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>118672115</v>
+        <v>118683020</v>
       </c>
       <c r="B216" t="n">
-        <v>78136</v>
+        <v>91780</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -23408,37 +23408,37 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken (Anna-Lisabäcken), Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>697004</v>
+        <v>696836</v>
       </c>
       <c r="R216" t="n">
-        <v>7323588</v>
+        <v>7323512</v>
       </c>
       <c r="S216" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -23482,12 +23482,12 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -23714,10 +23714,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119914656</v>
+        <v>119914542</v>
       </c>
       <c r="B219" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23726,25 +23726,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23760,7 +23760,7 @@
         <v>7323606</v>
       </c>
       <c r="S219" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -23826,10 +23826,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119926679</v>
+        <v>119914656</v>
       </c>
       <c r="B220" t="n">
-        <v>89230</v>
+        <v>91840</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23838,52 +23838,41 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>696839</v>
+        <v>696718</v>
       </c>
       <c r="R220" t="n">
-        <v>7323694</v>
+        <v>7323606</v>
       </c>
       <c r="S220" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -23910,18 +23899,27 @@
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AD220" t="b">
         <v>0</v>
       </c>
       <c r="AE220" t="b">
         <v>0</v>
       </c>
-      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -23940,10 +23938,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119914403</v>
+        <v>119926679</v>
       </c>
       <c r="B221" t="n">
-        <v>91834</v>
+        <v>89230</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23952,41 +23950,52 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4362</v>
+        <v>1596</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>696718</v>
+        <v>696839</v>
       </c>
       <c r="R221" t="n">
-        <v>7323606</v>
+        <v>7323694</v>
       </c>
       <c r="S221" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24013,27 +24022,18 @@
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AD221" t="b">
         <v>0</v>
       </c>
       <c r="AE221" t="b">
         <v>0</v>
       </c>
+      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -24052,10 +24052,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119914542</v>
+        <v>119914403</v>
       </c>
       <c r="B222" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -24068,21 +24068,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -23714,10 +23714,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119914542</v>
+        <v>119914432</v>
       </c>
       <c r="B219" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23726,25 +23726,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23760,7 +23760,7 @@
         <v>7323606</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -23826,10 +23826,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119914656</v>
+        <v>119926679</v>
       </c>
       <c r="B220" t="n">
-        <v>91840</v>
+        <v>89230</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23838,41 +23838,52 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>696718</v>
+        <v>696839</v>
       </c>
       <c r="R220" t="n">
-        <v>7323606</v>
+        <v>7323694</v>
       </c>
       <c r="S220" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -23899,27 +23910,18 @@
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AD220" t="b">
         <v>0</v>
       </c>
       <c r="AE220" t="b">
         <v>0</v>
       </c>
+      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -23938,10 +23940,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119926679</v>
+        <v>119914542</v>
       </c>
       <c r="B221" t="n">
-        <v>89230</v>
+        <v>91826</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23950,52 +23952,41 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1596</v>
+        <v>3100</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>696839</v>
+        <v>696718</v>
       </c>
       <c r="R221" t="n">
-        <v>7323694</v>
+        <v>7323606</v>
       </c>
       <c r="S221" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24022,18 +24013,27 @@
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AD221" t="b">
         <v>0</v>
       </c>
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -23714,7 +23714,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119914432</v>
+        <v>119914656</v>
       </c>
       <c r="B219" t="n">
         <v>91840</v>
@@ -23826,10 +23826,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119926679</v>
+        <v>119914542</v>
       </c>
       <c r="B220" t="n">
-        <v>89230</v>
+        <v>91826</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23838,52 +23838,41 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1596</v>
+        <v>3100</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>696839</v>
+        <v>696718</v>
       </c>
       <c r="R220" t="n">
-        <v>7323694</v>
+        <v>7323606</v>
       </c>
       <c r="S220" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -23910,18 +23899,27 @@
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AD220" t="b">
         <v>0</v>
       </c>
       <c r="AE220" t="b">
         <v>0</v>
       </c>
-      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -23940,10 +23938,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119914542</v>
+        <v>119926679</v>
       </c>
       <c r="B221" t="n">
-        <v>91826</v>
+        <v>89230</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23952,41 +23950,52 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>3100</v>
+        <v>1596</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>696718</v>
+        <v>696839</v>
       </c>
       <c r="R221" t="n">
-        <v>7323606</v>
+        <v>7323694</v>
       </c>
       <c r="S221" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24013,27 +24022,18 @@
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AD221" t="b">
         <v>0</v>
       </c>
       <c r="AE221" t="b">
         <v>0</v>
       </c>
+      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -23714,10 +23714,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119914656</v>
+        <v>119914403</v>
       </c>
       <c r="B219" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23726,25 +23726,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23760,7 +23760,7 @@
         <v>7323606</v>
       </c>
       <c r="S219" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -23826,10 +23826,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119914542</v>
+        <v>119926679</v>
       </c>
       <c r="B220" t="n">
-        <v>91826</v>
+        <v>89247</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23838,41 +23838,52 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>3100</v>
+        <v>1596</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>696718</v>
+        <v>696839</v>
       </c>
       <c r="R220" t="n">
-        <v>7323606</v>
+        <v>7323694</v>
       </c>
       <c r="S220" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -23899,27 +23910,18 @@
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AD220" t="b">
         <v>0</v>
       </c>
       <c r="AE220" t="b">
         <v>0</v>
       </c>
+      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -23938,10 +23940,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119926679</v>
+        <v>119914542</v>
       </c>
       <c r="B221" t="n">
-        <v>89230</v>
+        <v>91844</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23950,52 +23952,41 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1596</v>
+        <v>3100</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>696839</v>
+        <v>696718</v>
       </c>
       <c r="R221" t="n">
-        <v>7323694</v>
+        <v>7323606</v>
       </c>
       <c r="S221" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24022,18 +24013,27 @@
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AD221" t="b">
         <v>0</v>
       </c>
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -24052,10 +24052,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119914403</v>
+        <v>119914432</v>
       </c>
       <c r="B222" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -24064,25 +24064,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -24098,7 +24098,7 @@
         <v>7323606</v>
       </c>
       <c r="S222" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -23714,10 +23714,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119914403</v>
+        <v>119914542</v>
       </c>
       <c r="B219" t="n">
-        <v>91852</v>
+        <v>91844</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23730,21 +23730,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23826,10 +23826,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119926679</v>
+        <v>119914656</v>
       </c>
       <c r="B220" t="n">
-        <v>89247</v>
+        <v>91858</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23838,52 +23838,41 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>696839</v>
+        <v>696718</v>
       </c>
       <c r="R220" t="n">
-        <v>7323694</v>
+        <v>7323606</v>
       </c>
       <c r="S220" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -23910,18 +23899,27 @@
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AD220" t="b">
         <v>0</v>
       </c>
       <c r="AE220" t="b">
         <v>0</v>
       </c>
-      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -23940,10 +23938,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119914542</v>
+        <v>119914403</v>
       </c>
       <c r="B221" t="n">
-        <v>91844</v>
+        <v>91852</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23956,21 +23954,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -24052,10 +24050,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119914432</v>
+        <v>119926679</v>
       </c>
       <c r="B222" t="n">
-        <v>91858</v>
+        <v>89247</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -24064,41 +24062,52 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>696718</v>
+        <v>696839</v>
       </c>
       <c r="R222" t="n">
-        <v>7323606</v>
+        <v>7323694</v>
       </c>
       <c r="S222" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -24125,27 +24134,18 @@
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AD222" t="b">
         <v>0</v>
       </c>
       <c r="AE222" t="b">
         <v>0</v>
       </c>
+      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -23938,10 +23938,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119914403</v>
+        <v>119926679</v>
       </c>
       <c r="B221" t="n">
-        <v>91852</v>
+        <v>89247</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23950,41 +23950,52 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4362</v>
+        <v>1596</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>696718</v>
+        <v>696839</v>
       </c>
       <c r="R221" t="n">
-        <v>7323606</v>
+        <v>7323694</v>
       </c>
       <c r="S221" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24011,27 +24022,18 @@
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AD221" t="b">
         <v>0</v>
       </c>
       <c r="AE221" t="b">
         <v>0</v>
       </c>
+      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -24050,10 +24052,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119926679</v>
+        <v>119914403</v>
       </c>
       <c r="B222" t="n">
-        <v>89247</v>
+        <v>91852</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -24062,52 +24064,41 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1596</v>
+        <v>4362</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>696839</v>
+        <v>696718</v>
       </c>
       <c r="R222" t="n">
-        <v>7323694</v>
+        <v>7323606</v>
       </c>
       <c r="S222" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -24134,18 +24125,27 @@
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AD222" t="b">
         <v>0</v>
       </c>
       <c r="AE222" t="b">
         <v>0</v>
       </c>
-      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -23714,10 +23714,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119914542</v>
+        <v>119914432</v>
       </c>
       <c r="B219" t="n">
-        <v>91844</v>
+        <v>91858</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23726,25 +23726,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23760,7 +23760,7 @@
         <v>7323606</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -23826,10 +23826,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119914656</v>
+        <v>119914542</v>
       </c>
       <c r="B220" t="n">
-        <v>91858</v>
+        <v>91844</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23838,25 +23838,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -23872,7 +23872,7 @@
         <v>7323606</v>
       </c>
       <c r="S220" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -23714,10 +23714,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119914432</v>
+        <v>119914542</v>
       </c>
       <c r="B219" t="n">
-        <v>91858</v>
+        <v>91844</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23726,25 +23726,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23760,7 +23760,7 @@
         <v>7323606</v>
       </c>
       <c r="S219" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -23826,10 +23826,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119914542</v>
+        <v>119914432</v>
       </c>
       <c r="B220" t="n">
-        <v>91844</v>
+        <v>91858</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23838,25 +23838,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -23872,7 +23872,7 @@
         <v>7323606</v>
       </c>
       <c r="S220" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -23826,10 +23826,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119914432</v>
+        <v>119914403</v>
       </c>
       <c r="B220" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23838,25 +23838,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -23872,7 +23872,7 @@
         <v>7323606</v>
       </c>
       <c r="S220" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -23938,10 +23938,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119926679</v>
+        <v>119914656</v>
       </c>
       <c r="B221" t="n">
-        <v>89247</v>
+        <v>91858</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23950,52 +23950,41 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>696839</v>
+        <v>696718</v>
       </c>
       <c r="R221" t="n">
-        <v>7323694</v>
+        <v>7323606</v>
       </c>
       <c r="S221" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24022,18 +24011,27 @@
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AD221" t="b">
         <v>0</v>
       </c>
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -24052,10 +24050,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119914403</v>
+        <v>119926679</v>
       </c>
       <c r="B222" t="n">
-        <v>91852</v>
+        <v>89247</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -24064,41 +24062,52 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4362</v>
+        <v>1596</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>696718</v>
+        <v>696839</v>
       </c>
       <c r="R222" t="n">
-        <v>7323606</v>
+        <v>7323694</v>
       </c>
       <c r="S222" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -24125,27 +24134,18 @@
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AD222" t="b">
         <v>0</v>
       </c>
       <c r="AE222" t="b">
         <v>0</v>
       </c>
+      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -23714,10 +23714,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119914542</v>
+        <v>119926679</v>
       </c>
       <c r="B219" t="n">
-        <v>91844</v>
+        <v>89247</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23726,41 +23726,52 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>3100</v>
+        <v>1596</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>696718</v>
+        <v>696839</v>
       </c>
       <c r="R219" t="n">
-        <v>7323606</v>
+        <v>7323694</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -23787,27 +23798,18 @@
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="Z219" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AD219" t="b">
         <v>0</v>
       </c>
       <c r="AE219" t="b">
         <v>0</v>
       </c>
+      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -23938,7 +23940,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119914656</v>
+        <v>119914432</v>
       </c>
       <c r="B221" t="n">
         <v>91858</v>
@@ -24050,10 +24052,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119926679</v>
+        <v>119914542</v>
       </c>
       <c r="B222" t="n">
-        <v>89247</v>
+        <v>91844</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -24062,52 +24064,41 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1596</v>
+        <v>3100</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J222" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>696839</v>
+        <v>696718</v>
       </c>
       <c r="R222" t="n">
-        <v>7323694</v>
+        <v>7323606</v>
       </c>
       <c r="S222" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -24134,18 +24125,27 @@
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="AB222" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AD222" t="b">
         <v>0</v>
       </c>
       <c r="AE222" t="b">
         <v>0</v>
       </c>
-      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -23714,10 +23714,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119926679</v>
+        <v>119914542</v>
       </c>
       <c r="B219" t="n">
-        <v>89247</v>
+        <v>91844</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23726,52 +23726,41 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1596</v>
+        <v>3100</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>696839</v>
+        <v>696718</v>
       </c>
       <c r="R219" t="n">
-        <v>7323694</v>
+        <v>7323606</v>
       </c>
       <c r="S219" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -23798,18 +23787,27 @@
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="AD219" t="b">
         <v>0</v>
       </c>
       <c r="AE219" t="b">
         <v>0</v>
       </c>
-      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -23828,10 +23826,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119914403</v>
+        <v>119926679</v>
       </c>
       <c r="B220" t="n">
-        <v>91852</v>
+        <v>89247</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23840,41 +23838,52 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>4362</v>
+        <v>1596</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Järnvägsbro, Järnvägsbro, Pi lm</t>
+          <t>Järnvägsbro, Pi lm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>696718</v>
+        <v>696839</v>
       </c>
       <c r="R220" t="n">
-        <v>7323606</v>
+        <v>7323694</v>
       </c>
       <c r="S220" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -23901,27 +23910,18 @@
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="AD220" t="b">
         <v>0</v>
       </c>
       <c r="AE220" t="b">
         <v>0</v>
       </c>
+      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -23940,7 +23940,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119914432</v>
+        <v>119914656</v>
       </c>
       <c r="B221" t="n">
         <v>91858</v>
@@ -24052,10 +24052,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119914542</v>
+        <v>119914403</v>
       </c>
       <c r="B222" t="n">
-        <v>91844</v>
+        <v>91852</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -24068,21 +24068,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -23069,11 +23069,11 @@
         <v>118682772</v>
       </c>
       <c r="B213" t="n">
-        <v>56504</v>
+        <v>56687</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -23183,11 +23183,11 @@
         <v>118684517</v>
       </c>
       <c r="B214" t="n">
-        <v>56504</v>
+        <v>56687</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -23069,7 +23069,7 @@
         <v>118682772</v>
       </c>
       <c r="B213" t="n">
-        <v>56687</v>
+        <v>56688</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>118684517</v>
       </c>
       <c r="B214" t="n">
-        <v>56687</v>
+        <v>56688</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -23069,7 +23069,7 @@
         <v>118682772</v>
       </c>
       <c r="B213" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>118684517</v>
       </c>
       <c r="B214" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY230"/>
+  <dimension ref="A1:AZ230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112728565</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118672804</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682709</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682710</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682929</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682930</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118671202</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118672115</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682711</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682814</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683797</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683798</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683799</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683800</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683801</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683802</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683803</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683804</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118684519</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683793</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2794,6 +2899,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683794</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2895,6 +3005,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683013</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2996,6 +3111,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683783</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3097,6 +3217,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683791</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3198,6 +3323,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683792</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3299,6 +3429,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118686843</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3400,6 +3535,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682694</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3501,6 +3641,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682696</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3602,6 +3747,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682697</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3701,6 +3851,11 @@
       <c r="AY31" t="inlineStr">
         <is>
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682704</t>
         </is>
       </c>
     </row>
@@ -3804,6 +3959,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112728502</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3905,6 +4065,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112728539</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4002,6 +4167,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118671603</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4103,6 +4273,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118672352</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4204,6 +4379,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118672765</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4305,6 +4485,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682706</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4406,6 +4591,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682707</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4507,6 +4697,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682708</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4608,6 +4803,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682774</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4709,6 +4909,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682775</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4810,6 +5015,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682811</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4911,6 +5121,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118673276</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5020,6 +5235,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119926679</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5121,6 +5341,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112728450</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5222,6 +5447,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112728456</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5323,6 +5553,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112728467</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5425,6 +5660,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682771</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5526,6 +5766,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682705</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5631,6 +5876,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118506630</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5733,6 +5983,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682773</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5840,6 +6095,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119914542</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5941,6 +6201,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682691</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6042,6 +6307,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118670832</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6143,6 +6413,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118671737</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6244,6 +6519,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118672105</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6345,6 +6625,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118673080</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6446,6 +6731,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682716</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6547,6 +6837,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682717</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6648,6 +6943,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682940</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6749,6 +7049,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682941</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6850,6 +7155,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682942</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6951,6 +7261,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683020</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7058,6 +7373,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119914403</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7163,6 +7483,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118506642</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7264,6 +7589,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118670735</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7365,6 +7695,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118671206</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7466,6 +7801,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118671444</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7567,6 +7907,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118672140</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7668,6 +8013,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118672428</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7769,6 +8119,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682712</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7870,6 +8225,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682713</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7971,6 +8331,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682816</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8072,6 +8437,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682818</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8173,6 +8543,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682820</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8274,6 +8649,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682931</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8375,6 +8755,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682932</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8476,6 +8861,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682933</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8577,6 +8967,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682934</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8678,6 +9073,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682935</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8779,6 +9179,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682936</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8880,6 +9285,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682937</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8981,6 +9391,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682938</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9082,6 +9497,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682939</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9183,6 +9603,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683014</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9284,6 +9709,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118686847</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9391,6 +9821,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119914432</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9492,6 +9927,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112728551</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9593,6 +10033,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682699</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9694,6 +10139,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683011</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9795,6 +10245,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118673032</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9897,6 +10352,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058986</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9999,6 +10459,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058987</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10100,6 +10565,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682692</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10201,6 +10671,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682765</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10302,6 +10777,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682923</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10403,6 +10883,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118671533</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10504,6 +10989,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683786</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10605,6 +11095,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118670883</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10706,6 +11201,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118673264</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10807,6 +11307,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682718</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10909,6 +11414,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682776</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11010,6 +11520,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682821</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11111,6 +11626,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682823</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11212,6 +11732,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682824</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11313,6 +11838,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682826</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11414,6 +11944,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682827</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11515,6 +12050,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682829</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11616,6 +12156,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682830</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11717,6 +12262,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682943</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11818,6 +12368,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682944</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11919,6 +12474,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682945</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12018,6 +12578,11 @@
       <c r="AY113" t="inlineStr">
         <is>
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682946</t>
         </is>
       </c>
     </row>
@@ -12125,6 +12690,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683010</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12227,6 +12797,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683021</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12329,6 +12904,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683022</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12431,6 +13011,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683023</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12533,6 +13118,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683024</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12635,6 +13225,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683025</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12737,6 +13332,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683026</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12839,6 +13439,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683027</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12941,6 +13546,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683028</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13043,6 +13653,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683029</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13145,6 +13760,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683030</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13247,6 +13867,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683031</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13348,6 +13973,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683809</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13449,6 +14079,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683811</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13550,6 +14185,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683812</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13651,6 +14291,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683813</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13752,6 +14397,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683814</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13853,6 +14503,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683815</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13954,6 +14609,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683816</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14055,6 +14715,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683817</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14156,6 +14821,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683818</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14257,6 +14927,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683820</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14358,6 +15033,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683821</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14459,6 +15139,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683822</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14560,6 +15245,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683823</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14661,6 +15351,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683824</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14762,6 +15457,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683826</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14863,6 +15563,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683827</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14964,6 +15669,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683828</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15065,6 +15775,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683829</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15166,6 +15881,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683830</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15267,6 +15987,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683831</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15368,6 +16093,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118684521</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15469,6 +16199,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118684523</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15570,6 +16305,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118684524</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15671,6 +16411,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118686848</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15772,6 +16517,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118686849</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15873,6 +16623,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118686850</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15974,6 +16729,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118686851</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16075,6 +16835,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118686852</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16176,6 +16941,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683003</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16277,6 +17047,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682927</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16378,6 +17153,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682928</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16479,6 +17259,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682693</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16580,6 +17365,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682766</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16681,6 +17471,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682770</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16782,6 +17577,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682809</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16883,6 +17683,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682915</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16984,6 +17789,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682916</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17085,6 +17895,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682918</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17186,6 +18001,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683004</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17287,6 +18107,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683005</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17388,6 +18213,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683756</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17489,6 +18319,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683758</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17590,6 +18425,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683760</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17691,6 +18531,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683761</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17792,6 +18637,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683762</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17893,6 +18743,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683763</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17994,6 +18849,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683764</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18095,6 +18955,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683765</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18196,6 +19061,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683766</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18297,6 +19167,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683768</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18398,6 +19273,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118684515</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18499,6 +19379,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118684516</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18600,6 +19485,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118686836</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18701,6 +19591,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118671958</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18802,6 +19697,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118673130</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18903,6 +19803,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682714</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19005,6 +19910,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682810</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19106,6 +20016,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683015</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19207,6 +20122,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683016</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19308,6 +20228,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683017</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19409,6 +20334,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683018</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19511,6 +20441,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683019</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19613,6 +20548,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683795</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19714,6 +20654,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683805</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19815,6 +20760,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683806</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19916,6 +20866,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683807</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20017,6 +20972,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683808</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20118,6 +21078,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118686845</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20219,6 +21184,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682698</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20320,6 +21290,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118672861</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20429,6 +21404,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682772</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20530,6 +21510,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118684517</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20631,6 +21616,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118685851</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20732,6 +21722,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682922</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20833,6 +21828,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682926</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20934,6 +21934,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683012</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21035,6 +22040,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683784</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21136,6 +22146,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683785</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21237,6 +22252,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118684518</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21338,6 +22358,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118671198</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21439,6 +22464,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118672026</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21540,6 +22570,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118673157</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21641,6 +22676,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682919</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21742,6 +22782,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682920</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21843,6 +22888,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118682921</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21945,6 +22995,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683006</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -22047,6 +23102,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683007</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -22149,6 +23209,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683008</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22250,6 +23315,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683009</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22351,6 +23421,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683770</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22452,6 +23527,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683771</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22553,6 +23633,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683772</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22654,6 +23739,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683774</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22755,6 +23845,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683775</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22856,6 +23951,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683776</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22957,6 +24057,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683777</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -23058,6 +24163,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683778</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -23159,6 +24269,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683779</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23260,6 +24375,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683780</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -23361,6 +24481,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683781</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23462,6 +24587,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683782</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23563,6 +24693,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118686837</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23662,6 +24797,11 @@
       <c r="AY228" t="inlineStr">
         <is>
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118686838</t>
         </is>
       </c>
     </row>
@@ -23769,6 +24909,11 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683788</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -23874,8 +25019,244 @@
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118683789</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -10256,7 +10256,7 @@
         <v>135058986</v>
       </c>
       <c r="B92" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>135058987</v>
       </c>
       <c r="B93" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 36411-2023 artfynd.xlsx
+++ b/artfynd/A 36411-2023 artfynd.xlsx
@@ -10256,7 +10256,7 @@
         <v>135058986</v>
       </c>
       <c r="B92" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>135058987</v>
       </c>
       <c r="B93" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
